--- a/otheragent/results/结果提交文件.xlsx
+++ b/otheragent/results/结果提交文件.xlsx
@@ -1156,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1164,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1206.3</v>
+        <v>1490.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.05976</v>
+        <v>2.27999</v>
       </c>
     </row>
     <row r="3">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1146.3</v>
+        <v>1358.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.21921</v>
+        <v>2.30807</v>
       </c>
     </row>
     <row r="4">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1146.3</v>
+        <v>1358.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2292.5</v>
+        <v>3051.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.21921</v>
+        <v>3.03178</v>
       </c>
     </row>
     <row r="5">
@@ -1327,32 +1327,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1206.3</v>
+        <v>1490.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2352.5</v>
+        <v>3515.3</v>
       </c>
       <c r="H5" t="n">
-        <v>1.21921</v>
+        <v>3.73421</v>
       </c>
     </row>
     <row r="6">
@@ -1363,32 +1363,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2332.2</v>
+        <v>3051.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S011→S015→S005</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3597</v>
+        <v>5972.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.22313</v>
+        <v>5.42523</v>
       </c>
     </row>
     <row r="7">
@@ -1399,32 +1399,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2352.5</v>
+        <v>3515.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S004→S008</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3557.4</v>
+        <v>6136.3</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2923</v>
+        <v>6.30729</v>
       </c>
     </row>
     <row r="8">
@@ -1435,32 +1435,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3557.4</v>
+        <v>5972.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S005→S008</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5072</v>
+        <v>8540.299999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08547</v>
+        <v>6.37084</v>
       </c>
     </row>
     <row r="9">
@@ -1471,32 +1471,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3597</v>
+        <v>6136.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S011→S009</t>
+          <t>S011→S007→S003→S006</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5474.1</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>2.10653</v>
+        <v>6.31517</v>
       </c>
     </row>
     <row r="10">
@@ -1507,32 +1507,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5072</v>
+        <v>8540.299999999999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S011→S015</t>
+          <t>S001→S009→S005</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7075.5</v>
+        <v>11081.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.27823</v>
+        <v>4.88214</v>
       </c>
     </row>
     <row r="11">
@@ -1543,32 +1543,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5474.1</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S001→S014</t>
+          <t>S004→S002</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7683.3</v>
+        <v>12071.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.28195</v>
+        <v>6.31965</v>
       </c>
     </row>
     <row r="12">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7075.5</v>
+        <v>11099</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S005→S015</t>
+          <t>S006→S007→S003</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9321.5</v>
+        <v>14078.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.50092</v>
+        <v>6.3727</v>
       </c>
     </row>
     <row r="13">
@@ -1615,32 +1615,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7683.3</v>
+        <v>12071.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S005→S009</t>
+          <t>S001→S002</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>9625</v>
+        <v>14435</v>
       </c>
       <c r="H13" t="n">
-        <v>2.61763</v>
+        <v>6.02199</v>
       </c>
     </row>
     <row r="14">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9321.5</v>
+        <v>14078.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S004→S008</t>
+          <t>S013→S012</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>11651.4</v>
+        <v>16380.8</v>
       </c>
       <c r="H14" t="n">
-        <v>2.92255</v>
+        <v>5.08164</v>
       </c>
     </row>
     <row r="15">
@@ -1687,32 +1687,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9625</v>
+        <v>14616.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S005→S003</t>
+          <t>S010→S013→S012→S009</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>12187.1</v>
+        <v>17888.9</v>
       </c>
       <c r="H15" t="n">
-        <v>3.06785</v>
+        <v>6.39574</v>
       </c>
     </row>
     <row r="16">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11651.4</v>
+        <v>16637.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S007→S002</t>
+          <t>S001→S002</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>14136.2</v>
+        <v>18934.8</v>
       </c>
       <c r="H16" t="n">
-        <v>3.15424</v>
+        <v>5.12056</v>
       </c>
     </row>
     <row r="17">
@@ -1759,716 +1759,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12187.1</v>
+        <v>17888.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S001→S008</t>
+          <t>S006→S003</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>14356.2</v>
+        <v>20610.4</v>
       </c>
       <c r="H17" t="n">
-        <v>2.83485</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>14136.2</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S006→S003</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>16455.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.65676</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>T018</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>14356.2</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>S004</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>16278.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.03546</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>T019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>16278.3</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>18286.7</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2.93121</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>16455.2</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>S001→S002</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>18423.4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.60015</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>T021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>18286.7</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>20040.6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.86897</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>T022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>18423.4</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S004→S008</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>20813.3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.10906</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>20216.8</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>22285.2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.54912</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>20813.3</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S001→S002</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>22781.4</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.42047</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>22285.2</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S001→S002</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>24313.3</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.37839</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>22827.2</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S007</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>24389.6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.87313</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>T027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>24313.3</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S010→S007</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>26627</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.79581</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>T028</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>24497</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S013→S012→S002</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>27054.3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>3.00123</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>T029</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>26627</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S005→S004</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>28780.8</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2.61044</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>T030</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>27054.3</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S007→S003→S015</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>29537.9</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2.88281</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>T031</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>28780.8</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S010</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>30271.8</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.63421</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>T032</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>29537.9</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S014</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>31339</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.92129</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>T033</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>30578.7</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S013→S012</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>32662</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2.80974</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>T034</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>31453.8</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S011→S008</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>33651.2</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.74665</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>T035</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>32662</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S002→S012→S013</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>35219.3</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3.10204</v>
+        <v>5.3764</v>
       </c>
     </row>
   </sheetData>
@@ -2521,7 +1837,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2530,7 +1846,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>916.3</v>
+        <v>1048.5</v>
       </c>
     </row>
     <row r="3">
@@ -2550,7 +1866,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>916.3</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="4">
@@ -2561,7 +1877,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T025</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2570,7 +1886,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23171.4</v>
+        <v>13072.4</v>
       </c>
     </row>
     <row r="5">
@@ -2581,7 +1897,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2590,7 +1906,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13013.3</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="6">
@@ -2601,7 +1917,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2610,7 +1926,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6300.4</v>
+        <v>17680.1</v>
       </c>
     </row>
     <row r="7">
@@ -2621,7 +1937,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T025</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2630,7 +1946,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23171.4</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="8">
@@ -2650,7 +1966,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>916.3</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="9">
@@ -2661,7 +1977,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T024</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2670,7 +1986,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21639.6</v>
+        <v>17680.1</v>
       </c>
     </row>
     <row r="10">
@@ -2681,7 +1997,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2690,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>856.3</v>
+        <v>17680.1</v>
       </c>
     </row>
     <row r="11">
@@ -2701,7 +2017,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2710,7 +2026,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>856.3</v>
+        <v>9510.799999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2721,7 +2037,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2730,7 +2046,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2002.5</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="13">
@@ -2741,7 +2057,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2750,7 +2066,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2002.5</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="14">
@@ -2761,7 +2077,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2770,7 +2086,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2062.5</v>
+        <v>1048.5</v>
       </c>
     </row>
     <row r="15">
@@ -2781,7 +2097,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2790,7 +2106,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2062.5</v>
+        <v>1048.5</v>
       </c>
     </row>
     <row r="16">
@@ -2801,7 +2117,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2810,7 +2126,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17281.5</v>
+        <v>1048.5</v>
       </c>
     </row>
     <row r="17">
@@ -2821,7 +2137,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T025</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2830,7 +2146,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23718.3</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="18">
@@ -2841,7 +2157,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T024</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2850,7 +2166,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22186.4</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="19">
@@ -2861,7 +2177,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2870,7 +2186,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13541.2</v>
+        <v>11453.1</v>
       </c>
     </row>
     <row r="20">
@@ -2881,7 +2197,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T028</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2890,7 +2206,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26459.3</v>
+        <v>18316</v>
       </c>
     </row>
     <row r="21">
@@ -2901,7 +2217,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T035</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2910,7 +2226,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33820.9</v>
+        <v>18316</v>
       </c>
     </row>
     <row r="22">
@@ -2921,7 +2237,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2930,7 +2246,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17828.4</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="23">
@@ -2941,7 +2257,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2950,7 +2266,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19445.6</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="24">
@@ -2961,7 +2277,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2970,7 +2286,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19445.6</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="25">
@@ -2981,7 +2297,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2990,7 +2306,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21558.9</v>
+        <v>8322.799999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3001,7 +2317,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3010,7 +2326,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>21558.9</v>
+        <v>8322.799999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3021,7 +2337,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3030,7 +2346,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11460.8</v>
+        <v>8322.799999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3041,7 +2357,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3050,7 +2366,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21558.9</v>
+        <v>19827.2</v>
       </c>
     </row>
     <row r="29">
@@ -3061,7 +2377,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>T030</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3070,7 +2386,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28520.6</v>
+        <v>19827.2</v>
       </c>
     </row>
     <row r="30">
@@ -3081,7 +2397,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3090,7 +2406,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17560.4</v>
+        <v>13295.2</v>
       </c>
     </row>
     <row r="31">
@@ -3101,7 +2417,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3110,7 +2426,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17560.4</v>
+        <v>13295.2</v>
       </c>
     </row>
     <row r="32">
@@ -3121,7 +2437,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3130,7 +2446,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15729</v>
+        <v>8322.799999999999</v>
       </c>
     </row>
     <row r="33">
@@ -3141,7 +2457,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3150,7 +2466,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>19696</v>
+        <v>10989.9</v>
       </c>
     </row>
     <row r="34">
@@ -3161,7 +2477,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3170,7 +2486,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10534.1</v>
+        <v>10989.9</v>
       </c>
     </row>
     <row r="35">
@@ -3181,7 +2497,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3190,7 +2506,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>19696</v>
+        <v>4895.1</v>
       </c>
     </row>
     <row r="36">
@@ -3201,7 +2517,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>T029</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3210,7 +2526,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28101.5</v>
+        <v>4895.1</v>
       </c>
     </row>
     <row r="37">
@@ -3221,7 +2537,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3230,7 +2546,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15598.9</v>
+        <v>10989.9</v>
       </c>
     </row>
     <row r="38">
@@ -3241,7 +2557,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3250,7 +2566,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15598.9</v>
+        <v>10989.9</v>
       </c>
     </row>
     <row r="39">
@@ -3261,7 +2577,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3270,7 +2586,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10635.1</v>
+        <v>7236.9</v>
       </c>
     </row>
     <row r="40">
@@ -3281,7 +2597,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3290,7 +2606,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8085.6</v>
+        <v>5469.6</v>
       </c>
     </row>
     <row r="41">
@@ -3301,7 +2617,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>T029</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3310,7 +2626,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>27637.1</v>
+        <v>10578.8</v>
       </c>
     </row>
     <row r="42">
@@ -3321,7 +2637,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3330,7 +2646,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8693.299999999999</v>
+        <v>10578.8</v>
       </c>
     </row>
     <row r="43">
@@ -3350,7 +2666,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4597.5</v>
+        <v>7236.9</v>
       </c>
     </row>
     <row r="44">
@@ -3370,7 +2686,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4597.5</v>
+        <v>7236.9</v>
       </c>
     </row>
     <row r="45">
@@ -3381,7 +2697,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3390,7 +2706,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3273.4</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="46">
@@ -3401,7 +2717,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3410,7 +2726,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14987.4</v>
+        <v>9157.5</v>
       </c>
     </row>
     <row r="47">
@@ -3421,7 +2737,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3430,7 +2746,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3273.4</v>
+        <v>18958.9</v>
       </c>
     </row>
     <row r="48">
@@ -3441,7 +2757,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3450,7 +2766,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3273.4</v>
+        <v>18958.9</v>
       </c>
     </row>
     <row r="49">
@@ -3461,7 +2777,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3470,7 +2786,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3233.7</v>
+        <v>18958.9</v>
       </c>
     </row>
     <row r="50">
@@ -3481,7 +2797,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3490,7 +2806,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3233.7</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="51">
@@ -3501,7 +2817,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>T030</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3510,7 +2826,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>28113.1</v>
+        <v>12805.3</v>
       </c>
     </row>
     <row r="52">
@@ -3521,7 +2837,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3530,7 +2846,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12680.3</v>
+        <v>7760.9</v>
       </c>
     </row>
     <row r="53">
@@ -3541,7 +2857,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>T027</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3550,7 +2866,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26123.5</v>
+        <v>2499.9</v>
       </c>
     </row>
     <row r="54">
@@ -3561,7 +2877,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3570,7 +2886,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>23886.1</v>
+        <v>2499.9</v>
       </c>
     </row>
     <row r="55">
@@ -3581,7 +2897,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3590,7 +2906,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>23886.1</v>
+        <v>12805.3</v>
       </c>
     </row>
     <row r="56">
@@ -3601,7 +2917,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3610,7 +2926,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>20146.8</v>
+        <v>7843.4</v>
       </c>
     </row>
     <row r="57">
@@ -3621,7 +2937,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3630,7 +2946,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10984.9</v>
+        <v>7843.4</v>
       </c>
     </row>
     <row r="58">
@@ -3641,7 +2957,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T034</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3650,7 +2966,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>32984.7</v>
+        <v>5439.5</v>
       </c>
     </row>
     <row r="59">
@@ -3661,7 +2977,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T034</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3670,7 +2986,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>32984.7</v>
+        <v>5439.5</v>
       </c>
     </row>
     <row r="60">
@@ -3681,7 +2997,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3690,7 +3006,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13689.7</v>
+        <v>7843.4</v>
       </c>
     </row>
     <row r="61">
@@ -3701,7 +3017,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3710,7 +3026,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5007</v>
+        <v>17401.2</v>
       </c>
     </row>
     <row r="62">
@@ -3721,7 +3037,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3730,7 +3046,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5007</v>
+        <v>10014.4</v>
       </c>
     </row>
     <row r="63">
@@ -3741,7 +3057,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3750,7 +3066,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9157.9</v>
+        <v>10014.4</v>
       </c>
     </row>
     <row r="64">
@@ -3761,7 +3077,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T027</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3770,7 +3086,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>25306.3</v>
+        <v>15896.3</v>
       </c>
     </row>
     <row r="65">
@@ -3781,7 +3097,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>T031</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3790,7 +3106,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>29803.9</v>
+        <v>15896.3</v>
       </c>
     </row>
     <row r="66">
@@ -3801,7 +3117,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T031</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3810,7 +3126,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>29803.9</v>
+        <v>15896.3</v>
       </c>
     </row>
     <row r="67">
@@ -3830,7 +3146,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4441.8</v>
+        <v>7222.2</v>
       </c>
     </row>
     <row r="68">
@@ -3841,7 +3157,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>T034</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3850,7 +3166,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>32298.6</v>
+        <v>7222.2</v>
       </c>
     </row>
     <row r="69">
@@ -3861,7 +3177,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3870,7 +3186,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5886.8</v>
+        <v>4011.1</v>
       </c>
     </row>
     <row r="70">
@@ -3881,7 +3197,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T028</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3890,7 +3206,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>25958.8</v>
+        <v>16892.1</v>
       </c>
     </row>
     <row r="71">
@@ -3901,7 +3217,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>T035</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3910,7 +3226,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>34317.3</v>
+        <v>15691.9</v>
       </c>
     </row>
     <row r="72">
@@ -3921,7 +3237,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>T033</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3930,7 +3246,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>32010.5</v>
+        <v>15691.9</v>
       </c>
     </row>
     <row r="73">
@@ -3941,7 +3257,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>T028</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3950,7 +3266,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25496.9</v>
+        <v>16372.8</v>
       </c>
     </row>
     <row r="74">
@@ -3961,7 +3277,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>T035</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3970,7 +3286,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>34774.5</v>
+        <v>16372.8</v>
       </c>
     </row>
     <row r="75">
@@ -3981,7 +3297,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>T033</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3990,7 +3306,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>31548.6</v>
+        <v>15136.5</v>
       </c>
     </row>
     <row r="76">
@@ -4001,7 +3317,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4010,7 +3326,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7060.3</v>
+        <v>2830.9</v>
       </c>
     </row>
     <row r="77">
@@ -4021,7 +3337,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>T032</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4030,7 +3346,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30716</v>
+        <v>2830.9</v>
       </c>
     </row>
     <row r="78">
@@ -4041,7 +3357,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>T032</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4050,7 +3366,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30716</v>
+        <v>2830.9</v>
       </c>
     </row>
     <row r="79">
@@ -4061,7 +3377,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4070,7 +3386,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8713.200000000001</v>
+        <v>4735.7</v>
       </c>
     </row>
     <row r="80">
@@ -4081,7 +3397,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>T030</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4090,7 +3406,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28929.6</v>
+        <v>4735.7</v>
       </c>
     </row>
     <row r="81">
@@ -4101,7 +3417,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4110,7 +3426,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6467.2</v>
+        <v>4735.7</v>
       </c>
     </row>
   </sheetData>
@@ -4124,7 +3440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4217,25 +3533,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>109.2388</v>
+        <v>109.215383</v>
       </c>
       <c r="F2" t="n">
-        <v>23.006658</v>
+        <v>23.028329</v>
       </c>
       <c r="G2" t="n">
-        <v>440.6</v>
+        <v>562.1</v>
       </c>
       <c r="H2" t="n">
-        <v>298.4</v>
+        <v>452.7</v>
       </c>
       <c r="I2" t="n">
-        <v>5072</v>
+        <v>3051.2</v>
       </c>
       <c r="J2" t="n">
-        <v>5171.2</v>
+        <v>3314.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4001</v>
+        <v>0.5446</v>
       </c>
     </row>
     <row r="3">
@@ -4258,25 +3574,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>109.230994</v>
+        <v>109.266119</v>
       </c>
       <c r="F3" t="n">
         <v>23.010269</v>
       </c>
       <c r="G3" t="n">
-        <v>395.2</v>
+        <v>559</v>
       </c>
       <c r="H3" t="n">
-        <v>239.9</v>
+        <v>525.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5474.1</v>
+        <v>3515.3</v>
       </c>
       <c r="J3" t="n">
-        <v>5509.7</v>
+        <v>3855.4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4687</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="4">
@@ -4296,28 +3612,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5171.2</v>
+        <v>3314.7</v>
       </c>
       <c r="E4" t="n">
-        <v>109.219286</v>
+        <v>109.207577</v>
       </c>
       <c r="F4" t="n">
-        <v>23.006658</v>
+        <v>23.028329</v>
       </c>
       <c r="G4" t="n">
-        <v>460.5</v>
+        <v>599.6</v>
       </c>
       <c r="H4" t="n">
-        <v>5499.5</v>
+        <v>3812</v>
       </c>
       <c r="I4" t="n">
-        <v>7075.5</v>
+        <v>5972.6</v>
       </c>
       <c r="J4" t="n">
-        <v>7206.4</v>
+        <v>6283.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5463</v>
+        <v>0.8236</v>
       </c>
     </row>
     <row r="5">
@@ -4337,28 +3653,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5509.7</v>
+        <v>3855.4</v>
       </c>
       <c r="E5" t="n">
-        <v>109.266119</v>
+        <v>109.242702</v>
       </c>
       <c r="F5" t="n">
-        <v>23.010269</v>
+        <v>23.060836</v>
       </c>
       <c r="G5" t="n">
-        <v>559</v>
+        <v>555.5</v>
       </c>
       <c r="H5" t="n">
-        <v>6035.1</v>
+        <v>4527</v>
       </c>
       <c r="I5" t="n">
-        <v>7683.3</v>
+        <v>6136.3</v>
       </c>
       <c r="J5" t="n">
-        <v>8023.4</v>
+        <v>6620.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6842</v>
+        <v>0.7677</v>
       </c>
     </row>
     <row r="6">
@@ -4378,28 +3694,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7206.4</v>
+        <v>6283.7</v>
       </c>
       <c r="E6" t="n">
-        <v>109.207577</v>
+        <v>109.203674</v>
       </c>
       <c r="F6" t="n">
-        <v>23.028329</v>
+        <v>23.039165</v>
       </c>
       <c r="G6" t="n">
-        <v>599.6</v>
+        <v>705.6</v>
       </c>
       <c r="H6" t="n">
-        <v>7703.8</v>
+        <v>6880.9</v>
       </c>
       <c r="I6" t="n">
-        <v>9321.5</v>
+        <v>8540.299999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>9632.6</v>
+        <v>8959</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6577</v>
+        <v>0.7277</v>
       </c>
     </row>
     <row r="7">
@@ -4419,28 +3735,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8023.4</v>
+        <v>6620.2</v>
       </c>
       <c r="E7" t="n">
-        <v>109.2388</v>
+        <v>109.203674</v>
       </c>
       <c r="F7" t="n">
-        <v>23.006658</v>
+        <v>23.021105</v>
       </c>
       <c r="G7" t="n">
-        <v>440.6</v>
+        <v>614</v>
       </c>
       <c r="H7" t="n">
-        <v>8321.799999999999</v>
+        <v>7109.6</v>
       </c>
       <c r="I7" t="n">
-        <v>9625</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>9724.200000000001</v>
+        <v>9811.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4455</v>
+        <v>0.8911</v>
       </c>
     </row>
     <row r="8">
@@ -4460,28 +3776,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9632.6</v>
+        <v>8959</v>
       </c>
       <c r="E8" t="n">
-        <v>109.242702</v>
+        <v>109.2388</v>
       </c>
       <c r="F8" t="n">
-        <v>23.060836</v>
+        <v>23.006658</v>
       </c>
       <c r="G8" t="n">
-        <v>555.5</v>
+        <v>440.6</v>
       </c>
       <c r="H8" t="n">
-        <v>10304.1</v>
+        <v>9257.4</v>
       </c>
       <c r="I8" t="n">
-        <v>11651.4</v>
+        <v>11081.8</v>
       </c>
       <c r="J8" t="n">
-        <v>12135.3</v>
+        <v>11181</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6876</v>
+        <v>0.6047</v>
       </c>
     </row>
     <row r="9">
@@ -4501,28 +3817,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9724.200000000001</v>
+        <v>9811.6</v>
       </c>
       <c r="E9" t="n">
-        <v>109.203674</v>
+        <v>109.234897</v>
       </c>
       <c r="F9" t="n">
-        <v>23.024717</v>
+        <v>23.060836</v>
       </c>
       <c r="G9" t="n">
-        <v>663.2</v>
+        <v>552.3</v>
       </c>
       <c r="H9" t="n">
-        <v>10239.1</v>
+        <v>10469.5</v>
       </c>
       <c r="I9" t="n">
-        <v>12187.1</v>
+        <v>12071.9</v>
       </c>
       <c r="J9" t="n">
-        <v>12519.8</v>
+        <v>12540.1</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7662</v>
+        <v>0.7586000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -4542,28 +3858,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12135.3</v>
+        <v>11181</v>
       </c>
       <c r="E10" t="n">
-        <v>109.219286</v>
+        <v>109.207577</v>
       </c>
       <c r="F10" t="n">
-        <v>23.035553</v>
+        <v>23.021105</v>
       </c>
       <c r="G10" t="n">
-        <v>494.8</v>
+        <v>541.6</v>
       </c>
       <c r="H10" t="n">
-        <v>12601.8</v>
+        <v>11631.2</v>
       </c>
       <c r="I10" t="n">
-        <v>14136.2</v>
+        <v>14078.3</v>
       </c>
       <c r="J10" t="n">
-        <v>14406.6</v>
+        <v>14337.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6209</v>
+        <v>0.8854</v>
       </c>
     </row>
     <row r="11">
@@ -4583,28 +3899,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12519.8</v>
+        <v>12540.1</v>
       </c>
       <c r="E11" t="n">
-        <v>109.203674</v>
+        <v>109.219286</v>
       </c>
       <c r="F11" t="n">
-        <v>23.039165</v>
+        <v>23.035553</v>
       </c>
       <c r="G11" t="n">
-        <v>705.6</v>
+        <v>494.8</v>
       </c>
       <c r="H11" t="n">
-        <v>13117.1</v>
+        <v>13006.6</v>
       </c>
       <c r="I11" t="n">
-        <v>14356.2</v>
+        <v>14435</v>
       </c>
       <c r="J11" t="n">
-        <v>14775</v>
+        <v>14705.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5885</v>
       </c>
     </row>
     <row r="12">
@@ -4624,28 +3940,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14406.6</v>
+        <v>14337.2</v>
       </c>
       <c r="E12" t="n">
-        <v>109.203674</v>
+        <v>109.262217</v>
       </c>
       <c r="F12" t="n">
         <v>23.017493</v>
       </c>
       <c r="G12" t="n">
-        <v>653.1</v>
+        <v>572.1</v>
       </c>
       <c r="H12" t="n">
-        <v>14895.2</v>
+        <v>14837.7</v>
       </c>
       <c r="I12" t="n">
-        <v>16455.2</v>
+        <v>16380.8</v>
       </c>
       <c r="J12" t="n">
-        <v>16760.9</v>
+        <v>16693.4</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="13">
@@ -4665,28 +3981,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14775</v>
+        <v>14705.5</v>
       </c>
       <c r="E13" t="n">
-        <v>109.234897</v>
+        <v>109.273925</v>
       </c>
       <c r="F13" t="n">
-        <v>23.060836</v>
+        <v>23.039165</v>
       </c>
       <c r="G13" t="n">
-        <v>552.3</v>
+        <v>597.1</v>
       </c>
       <c r="H13" t="n">
-        <v>15432.9</v>
+        <v>15354.1</v>
       </c>
       <c r="I13" t="n">
-        <v>16278.3</v>
+        <v>17888.9</v>
       </c>
       <c r="J13" t="n">
-        <v>16746.4</v>
+        <v>18350</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5273</v>
+        <v>1.0357</v>
       </c>
     </row>
     <row r="14">
@@ -4697,7 +4013,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4706,28 +4022,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16746.4</v>
+        <v>16693.4</v>
       </c>
       <c r="E14" t="n">
         <v>109.219286</v>
       </c>
       <c r="F14" t="n">
-        <v>23.017493</v>
+        <v>23.035553</v>
       </c>
       <c r="G14" t="n">
-        <v>511.8</v>
+        <v>494.8</v>
       </c>
       <c r="H14" t="n">
-        <v>17112.7</v>
+        <v>17159.9</v>
       </c>
       <c r="I14" t="n">
-        <v>18286.7</v>
+        <v>18934.8</v>
       </c>
       <c r="J14" t="n">
-        <v>18460.6</v>
+        <v>19205.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4435</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="15">
@@ -4738,7 +4054,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4747,684 +4063,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16760.9</v>
+        <v>18350</v>
       </c>
       <c r="E15" t="n">
-        <v>109.219286</v>
+        <v>109.203674</v>
       </c>
       <c r="F15" t="n">
-        <v>23.035553</v>
+        <v>23.017493</v>
       </c>
       <c r="G15" t="n">
-        <v>494.8</v>
+        <v>653.1</v>
       </c>
       <c r="H15" t="n">
-        <v>17227.4</v>
+        <v>18838.6</v>
       </c>
       <c r="I15" t="n">
-        <v>18423.4</v>
+        <v>20610.4</v>
       </c>
       <c r="J15" t="n">
-        <v>18693.8</v>
+        <v>20916.1</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5175</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>RT15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>R-P03</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>18460.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F16" t="n">
-        <v>23.035553</v>
-      </c>
-      <c r="G16" t="n">
-        <v>494.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>18927.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>20040.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>20311</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.4923</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>RT16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>R-P04</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>18693.8</v>
-      </c>
-      <c r="E17" t="n">
-        <v>109.242702</v>
-      </c>
-      <c r="F17" t="n">
-        <v>23.060836</v>
-      </c>
-      <c r="G17" t="n">
-        <v>555.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>19365.3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>20813.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>21297.1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.7184</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>RT17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>R-P06</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>20311</v>
-      </c>
-      <c r="E18" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F18" t="n">
-        <v>23.017493</v>
-      </c>
-      <c r="G18" t="n">
-        <v>511.8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>20677.3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>22285.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>22459.1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.5760999999999999</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>RT18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>R-P05</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>21297.1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F19" t="n">
-        <v>23.035553</v>
-      </c>
-      <c r="G19" t="n">
-        <v>494.8</v>
-      </c>
-      <c r="H19" t="n">
-        <v>21763.7</v>
-      </c>
-      <c r="I19" t="n">
-        <v>22781.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>23051.9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.463</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>RT19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>R-P01</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>22459.1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F20" t="n">
-        <v>23.035553</v>
-      </c>
-      <c r="G20" t="n">
-        <v>494.8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>22925.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>24313.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>24583.7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.5760999999999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RT20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>R-P02</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>23051.9</v>
-      </c>
-      <c r="E21" t="n">
-        <v>109.215383</v>
-      </c>
-      <c r="F21" t="n">
-        <v>23.028329</v>
-      </c>
-      <c r="G21" t="n">
-        <v>562.1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>23504.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>24389.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>24653.1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.4079</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RT21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>R-P03</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>24583.7</v>
-      </c>
-      <c r="E22" t="n">
-        <v>109.273925</v>
-      </c>
-      <c r="F22" t="n">
-        <v>23.031941</v>
-      </c>
-      <c r="G22" t="n">
-        <v>562.3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>25203.5</v>
-      </c>
-      <c r="I22" t="n">
-        <v>27054.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>27486.8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>RT22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>R-P04</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>24653.1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F23" t="n">
-        <v>23.039165</v>
-      </c>
-      <c r="G23" t="n">
-        <v>528.6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>25153</v>
-      </c>
-      <c r="I23" t="n">
-        <v>26212.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>26519.3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.4948</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>RT23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>R-P06</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>26519.3</v>
-      </c>
-      <c r="E24" t="n">
-        <v>109.242702</v>
-      </c>
-      <c r="F24" t="n">
-        <v>23.006658</v>
-      </c>
-      <c r="G24" t="n">
-        <v>504.3</v>
-      </c>
-      <c r="H24" t="n">
-        <v>26855.6</v>
-      </c>
-      <c r="I24" t="n">
-        <v>26855.6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>26996.6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.0682</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RT24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>R-P05</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>26996.6</v>
-      </c>
-      <c r="E25" t="n">
-        <v>109.234897</v>
-      </c>
-      <c r="F25" t="n">
-        <v>23.060836</v>
-      </c>
-      <c r="G25" t="n">
-        <v>552.3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>27654.6</v>
-      </c>
-      <c r="I25" t="n">
-        <v>28780.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>29249</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.6132</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RT25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>R-P01</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>27486.8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>109.195869</v>
-      </c>
-      <c r="F26" t="n">
-        <v>23.021105</v>
-      </c>
-      <c r="G26" t="n">
-        <v>739.9</v>
-      </c>
-      <c r="H26" t="n">
-        <v>28061</v>
-      </c>
-      <c r="I26" t="n">
-        <v>29537.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>29938</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.6535</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RT26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>R-P02</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>29249</v>
-      </c>
-      <c r="E27" t="n">
-        <v>109.242702</v>
-      </c>
-      <c r="F27" t="n">
-        <v>23.006658</v>
-      </c>
-      <c r="G27" t="n">
-        <v>504.3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>29585.3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>30271.8</v>
-      </c>
-      <c r="J27" t="n">
-        <v>30412.8</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.2779</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>RT27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>R-P06</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>29938</v>
-      </c>
-      <c r="E28" t="n">
-        <v>109.266119</v>
-      </c>
-      <c r="F28" t="n">
-        <v>23.010269</v>
-      </c>
-      <c r="G28" t="n">
-        <v>559</v>
-      </c>
-      <c r="H28" t="n">
-        <v>30463.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>31339</v>
-      </c>
-      <c r="J28" t="n">
-        <v>31679.1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.4481</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RT28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>R-P04</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>30412.8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>109.262217</v>
-      </c>
-      <c r="F29" t="n">
-        <v>23.017493</v>
-      </c>
-      <c r="G29" t="n">
-        <v>572.1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>30913.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>32662</v>
-      </c>
-      <c r="J29" t="n">
-        <v>32974.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.6934</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RT29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>R-P03</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>31679.1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>109.203674</v>
-      </c>
-      <c r="F30" t="n">
-        <v>23.039165</v>
-      </c>
-      <c r="G30" t="n">
-        <v>705.6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>32276.3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>33651.2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>34070</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.6408</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>RT30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>R-P05</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>32974.6</v>
-      </c>
-      <c r="E31" t="n">
-        <v>109.273925</v>
-      </c>
-      <c r="F31" t="n">
-        <v>23.031941</v>
-      </c>
-      <c r="G31" t="n">
-        <v>562.3</v>
-      </c>
-      <c r="H31" t="n">
-        <v>33594.4</v>
-      </c>
-      <c r="I31" t="n">
-        <v>35219.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>35651.9</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.739</v>
+        <v>0.6963</v>
       </c>
     </row>
   </sheetData>
@@ -5438,7 +4098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5484,7 +4144,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5493,10 +4153,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>298.4</v>
+        <v>452.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5072</v>
+        <v>3051.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -5512,7 +4172,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5521,10 +4181,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>239.9</v>
+        <v>525.4</v>
       </c>
       <c r="D3" t="n">
-        <v>5474.1</v>
+        <v>3515.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -5540,7 +4200,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5549,10 +4209,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5499.5</v>
+        <v>3812</v>
       </c>
       <c r="D4" t="n">
-        <v>7075.5</v>
+        <v>5972.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -5568,7 +4228,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5577,10 +4237,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6035.1</v>
+        <v>4527</v>
       </c>
       <c r="D5" t="n">
-        <v>7683.3</v>
+        <v>6136.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -5596,7 +4256,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5605,10 +4265,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7703.8</v>
+        <v>6880.9</v>
       </c>
       <c r="D6" t="n">
-        <v>9321.5</v>
+        <v>8540.299999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -5624,7 +4284,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5633,10 +4293,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8321.799999999999</v>
+        <v>7109.6</v>
       </c>
       <c r="D7" t="n">
-        <v>9625</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5652,7 +4312,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5661,10 +4321,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10304.1</v>
+        <v>9257.4</v>
       </c>
       <c r="D8" t="n">
-        <v>11651.4</v>
+        <v>11081.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5680,7 +4340,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5689,10 +4349,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10239.1</v>
+        <v>10469.5</v>
       </c>
       <c r="D9" t="n">
-        <v>12187.1</v>
+        <v>12071.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5708,7 +4368,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5717,10 +4377,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12601.8</v>
+        <v>11631.2</v>
       </c>
       <c r="D10" t="n">
-        <v>14136.2</v>
+        <v>14078.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5736,7 +4396,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5745,10 +4405,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13117.1</v>
+        <v>13006.6</v>
       </c>
       <c r="D11" t="n">
-        <v>14356.2</v>
+        <v>14435</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -5764,7 +4424,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5773,10 +4433,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14895.2</v>
+        <v>14837.7</v>
       </c>
       <c r="D12" t="n">
-        <v>16455.2</v>
+        <v>16380.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -5792,7 +4452,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5801,10 +4461,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15432.9</v>
+        <v>15354.1</v>
       </c>
       <c r="D13" t="n">
-        <v>16278.3</v>
+        <v>17888.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -5820,7 +4480,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5829,10 +4489,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17112.7</v>
+        <v>17159.9</v>
       </c>
       <c r="D14" t="n">
-        <v>18286.7</v>
+        <v>18934.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -5848,7 +4508,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5857,10 +4517,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17227.4</v>
+        <v>18838.6</v>
       </c>
       <c r="D15" t="n">
-        <v>18423.4</v>
+        <v>20610.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -5870,454 +4530,6 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>RT14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>T021</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>18927.1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>20040.6</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>RT15</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>T022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>19365.3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>20813.3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>RT16</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>20677.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>22285.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>RT17</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>21763.7</v>
-      </c>
-      <c r="D19" t="n">
-        <v>22781.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>RT18</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>22925.6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>24313.3</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>RT19</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>23504.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>24389.6</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>RT20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>T028</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>25203.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>27054.3</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>RT21</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>T027</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>25153</v>
-      </c>
-      <c r="D23" t="n">
-        <v>26212.6</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>RT22</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>T027</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>26855.6</v>
-      </c>
-      <c r="D24" t="n">
-        <v>26855.6</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>RT23</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>T029</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>27654.6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>28780.8</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>RT24</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>T030</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>28061</v>
-      </c>
-      <c r="D26" t="n">
-        <v>29537.9</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>RT25</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>T031</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>29585.3</v>
-      </c>
-      <c r="D27" t="n">
-        <v>30271.8</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>RT26</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>T032</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>30463.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>31339</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>RT27</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>T033</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>30913.4</v>
-      </c>
-      <c r="D29" t="n">
-        <v>32662</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>RT28</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>T034</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>32276.3</v>
-      </c>
-      <c r="D30" t="n">
-        <v>33651.2</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>RT29</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>T035</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>33594.4</v>
-      </c>
-      <c r="D31" t="n">
-        <v>35219.3</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>RT30</t>
         </is>
       </c>
     </row>
@@ -6423,19 +4635,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -6462,19 +4674,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -6501,19 +4713,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -6533,32 +4745,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S001|S002|S003|S004|S005|S007|S008|S009|S010|S011|S012|S013|S015</t>
+          <t>S001|S002|S004|S005|S008|S009|S010|S012|S013</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6572,32 +4784,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S003|S006|S007|S011</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -6618,19 +4830,19 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>

--- a/otheragent/results/结果提交文件.xlsx
+++ b/otheragent/results/结果提交文件.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1156,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1164,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1206.3</v>
+        <v>1490.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.05976</v>
+        <v>2.27999</v>
       </c>
     </row>
     <row r="3">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1146.3</v>
+        <v>1358.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.21921</v>
+        <v>2.30807</v>
       </c>
     </row>
     <row r="4">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1146.3</v>
+        <v>1358.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2292.5</v>
+        <v>3051.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.21921</v>
+        <v>3.03178</v>
       </c>
     </row>
     <row r="5">
@@ -1327,32 +1327,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1206.3</v>
+        <v>1490.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2352.5</v>
+        <v>3515.3</v>
       </c>
       <c r="H5" t="n">
-        <v>1.21921</v>
+        <v>3.73421</v>
       </c>
     </row>
     <row r="6">
@@ -1363,32 +1363,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2332.2</v>
+        <v>3051.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S011→S015→S005</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3597</v>
+        <v>5972.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.22313</v>
+        <v>5.42523</v>
       </c>
     </row>
     <row r="7">
@@ -1399,32 +1399,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2352.5</v>
+        <v>3515.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S004→S008</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3557.4</v>
+        <v>6136.3</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2923</v>
+        <v>6.30729</v>
       </c>
     </row>
     <row r="8">
@@ -1435,32 +1435,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3557.4</v>
+        <v>5972.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S005→S008</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5072</v>
+        <v>8540.299999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08547</v>
+        <v>6.37084</v>
       </c>
     </row>
     <row r="9">
@@ -1471,32 +1471,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3597</v>
+        <v>6136.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S011→S009</t>
+          <t>S011→S007→S003→S006</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5474.1</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>2.10653</v>
+        <v>6.31517</v>
       </c>
     </row>
     <row r="10">
@@ -1507,32 +1507,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5072</v>
+        <v>8540.299999999999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S011→S015</t>
+          <t>S001→S009→S005</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7075.5</v>
+        <v>11081.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.27823</v>
+        <v>4.88214</v>
       </c>
     </row>
     <row r="11">
@@ -1543,32 +1543,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5474.1</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S001→S014</t>
+          <t>S004→S002</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7683.3</v>
+        <v>12071.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.28195</v>
+        <v>6.31965</v>
       </c>
     </row>
     <row r="12">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7075.5</v>
+        <v>11099</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S005→S015</t>
+          <t>S006→S007→S003</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9321.5</v>
+        <v>14078.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.50092</v>
+        <v>6.3727</v>
       </c>
     </row>
     <row r="13">
@@ -1615,32 +1615,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7683.3</v>
+        <v>12071.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S005→S009</t>
+          <t>S001→S002</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>9625</v>
+        <v>14435</v>
       </c>
       <c r="H13" t="n">
-        <v>2.61763</v>
+        <v>6.02199</v>
       </c>
     </row>
     <row r="14">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9321.5</v>
+        <v>14078.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S004→S008</t>
+          <t>S013→S012</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>11651.4</v>
+        <v>16380.8</v>
       </c>
       <c r="H14" t="n">
-        <v>2.92255</v>
+        <v>5.08164</v>
       </c>
     </row>
     <row r="15">
@@ -1687,32 +1687,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9625</v>
+        <v>14616.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S005→S003</t>
+          <t>S010→S013→S012→S009</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>12187.1</v>
+        <v>17888.9</v>
       </c>
       <c r="H15" t="n">
-        <v>3.06785</v>
+        <v>6.39574</v>
       </c>
     </row>
     <row r="16">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11651.4</v>
+        <v>16637.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S007→S002</t>
+          <t>S001→S002</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>14136.2</v>
+        <v>18934.8</v>
       </c>
       <c r="H16" t="n">
-        <v>3.15424</v>
+        <v>5.12056</v>
       </c>
     </row>
     <row r="17">
@@ -1759,716 +1759,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12187.1</v>
+        <v>17888.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S001→S008</t>
+          <t>S006→S003</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>14356.2</v>
+        <v>20610.4</v>
       </c>
       <c r="H17" t="n">
-        <v>2.83485</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>14136.2</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S006→S003</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>16455.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.65676</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>T018</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>14356.2</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>S004</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>16278.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.03546</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>T019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>16278.3</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>18286.7</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2.93121</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>16455.2</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>S001→S002</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>18423.4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.60015</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>T021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>18286.7</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>20040.6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.86897</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>T022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>18423.4</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S004→S008</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>20813.3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.10906</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>20216.8</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>22285.2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.54912</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>20813.3</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S001→S002</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>22781.4</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.42047</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>22285.2</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S001→S002</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>24313.3</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.37839</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>22827.2</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S007</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>24389.6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.87313</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>T027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>24313.3</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S010→S007</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>26627</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.79581</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>T028</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>24497</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S013→S012→S002</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>27054.3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>3.00123</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>T029</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>26627</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S005→S004</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>28780.8</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2.61044</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>T030</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>27054.3</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S007→S003→S015</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>29537.9</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2.88281</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>T031</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>28780.8</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S010</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>30271.8</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.63421</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>T032</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>29537.9</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S014</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>31339</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.92129</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>T033</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>B-B01</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>30578.7</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S013→S012</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>32662</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2.80974</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>T034</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>B-B02</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>31453.8</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S011→S008</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>33651.2</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.74665</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>T035</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>32662</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S002→S012→S013</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>35219.3</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3.10204</v>
+        <v>5.3764</v>
       </c>
     </row>
   </sheetData>
@@ -2521,7 +1837,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2530,7 +1846,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>916.3</v>
+        <v>1048.5</v>
       </c>
     </row>
     <row r="3">
@@ -2550,7 +1866,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>916.3</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="4">
@@ -2561,7 +1877,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T025</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2570,7 +1886,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23171.4</v>
+        <v>13072.4</v>
       </c>
     </row>
     <row r="5">
@@ -2581,7 +1897,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2590,7 +1906,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13013.3</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="6">
@@ -2601,7 +1917,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2610,7 +1926,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6300.4</v>
+        <v>17680.1</v>
       </c>
     </row>
     <row r="7">
@@ -2621,7 +1937,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T025</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2630,7 +1946,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23171.4</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="8">
@@ -2650,7 +1966,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>916.3</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="9">
@@ -2661,7 +1977,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T024</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2670,7 +1986,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21639.6</v>
+        <v>17680.1</v>
       </c>
     </row>
     <row r="10">
@@ -2681,7 +1997,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2690,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>856.3</v>
+        <v>17680.1</v>
       </c>
     </row>
     <row r="11">
@@ -2701,7 +2017,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2710,7 +2026,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>856.3</v>
+        <v>9510.799999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2721,7 +2037,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2730,7 +2046,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2002.5</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="13">
@@ -2741,7 +2057,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2750,7 +2066,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2002.5</v>
+        <v>1180.5</v>
       </c>
     </row>
     <row r="14">
@@ -2761,7 +2077,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2770,7 +2086,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2062.5</v>
+        <v>1048.5</v>
       </c>
     </row>
     <row r="15">
@@ -2781,7 +2097,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2790,7 +2106,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2062.5</v>
+        <v>1048.5</v>
       </c>
     </row>
     <row r="16">
@@ -2801,7 +2117,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2810,7 +2126,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17281.5</v>
+        <v>1048.5</v>
       </c>
     </row>
     <row r="17">
@@ -2821,7 +2137,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T025</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2830,7 +2146,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23718.3</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="18">
@@ -2841,7 +2157,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T024</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2850,7 +2166,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22186.4</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="19">
@@ -2861,7 +2177,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2870,7 +2186,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13541.2</v>
+        <v>11453.1</v>
       </c>
     </row>
     <row r="20">
@@ -2881,7 +2197,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T028</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2890,7 +2206,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26459.3</v>
+        <v>18316</v>
       </c>
     </row>
     <row r="21">
@@ -2901,7 +2217,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T035</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2910,7 +2226,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33820.9</v>
+        <v>18316</v>
       </c>
     </row>
     <row r="22">
@@ -2921,7 +2237,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2930,7 +2246,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17828.4</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="23">
@@ -2941,7 +2257,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2950,7 +2266,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19445.6</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="24">
@@ -2961,7 +2277,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2970,7 +2286,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19445.6</v>
+        <v>13816.3</v>
       </c>
     </row>
     <row r="25">
@@ -2981,7 +2297,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2990,7 +2306,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21558.9</v>
+        <v>8322.799999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3001,7 +2317,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3010,7 +2326,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>21558.9</v>
+        <v>8322.799999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3021,7 +2337,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3030,7 +2346,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11460.8</v>
+        <v>8322.799999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3041,7 +2357,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3050,7 +2366,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21558.9</v>
+        <v>19827.2</v>
       </c>
     </row>
     <row r="29">
@@ -3061,7 +2377,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>T030</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3070,7 +2386,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28520.6</v>
+        <v>19827.2</v>
       </c>
     </row>
     <row r="30">
@@ -3081,7 +2397,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3090,7 +2406,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17560.4</v>
+        <v>13295.2</v>
       </c>
     </row>
     <row r="31">
@@ -3101,7 +2417,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3110,7 +2426,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17560.4</v>
+        <v>13295.2</v>
       </c>
     </row>
     <row r="32">
@@ -3121,7 +2437,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3130,7 +2446,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15729</v>
+        <v>8322.799999999999</v>
       </c>
     </row>
     <row r="33">
@@ -3141,7 +2457,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3150,7 +2466,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>19696</v>
+        <v>10989.9</v>
       </c>
     </row>
     <row r="34">
@@ -3161,7 +2477,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3170,7 +2486,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10534.1</v>
+        <v>10989.9</v>
       </c>
     </row>
     <row r="35">
@@ -3181,7 +2497,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3190,7 +2506,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>19696</v>
+        <v>4895.1</v>
       </c>
     </row>
     <row r="36">
@@ -3201,7 +2517,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>T029</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3210,7 +2526,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28101.5</v>
+        <v>4895.1</v>
       </c>
     </row>
     <row r="37">
@@ -3221,7 +2537,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3230,7 +2546,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15598.9</v>
+        <v>10989.9</v>
       </c>
     </row>
     <row r="38">
@@ -3241,7 +2557,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3250,7 +2566,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15598.9</v>
+        <v>10989.9</v>
       </c>
     </row>
     <row r="39">
@@ -3261,7 +2577,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3270,7 +2586,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10635.1</v>
+        <v>7236.9</v>
       </c>
     </row>
     <row r="40">
@@ -3281,7 +2597,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3290,7 +2606,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8085.6</v>
+        <v>5469.6</v>
       </c>
     </row>
     <row r="41">
@@ -3301,7 +2617,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>T029</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3310,7 +2626,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>27637.1</v>
+        <v>10578.8</v>
       </c>
     </row>
     <row r="42">
@@ -3321,7 +2637,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3330,7 +2646,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8693.299999999999</v>
+        <v>10578.8</v>
       </c>
     </row>
     <row r="43">
@@ -3350,7 +2666,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4597.5</v>
+        <v>7236.9</v>
       </c>
     </row>
     <row r="44">
@@ -3370,7 +2686,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4597.5</v>
+        <v>7236.9</v>
       </c>
     </row>
     <row r="45">
@@ -3381,7 +2697,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3390,7 +2706,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3273.4</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="46">
@@ -3401,7 +2717,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3410,7 +2726,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14987.4</v>
+        <v>9157.5</v>
       </c>
     </row>
     <row r="47">
@@ -3421,7 +2737,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3430,7 +2746,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3273.4</v>
+        <v>18958.9</v>
       </c>
     </row>
     <row r="48">
@@ -3441,7 +2757,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3450,7 +2766,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3273.4</v>
+        <v>18958.9</v>
       </c>
     </row>
     <row r="49">
@@ -3461,7 +2777,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3470,7 +2786,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3233.7</v>
+        <v>18958.9</v>
       </c>
     </row>
     <row r="50">
@@ -3481,7 +2797,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3490,7 +2806,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3233.7</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="51">
@@ -3501,7 +2817,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>T030</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3510,7 +2826,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>28113.1</v>
+        <v>12805.3</v>
       </c>
     </row>
     <row r="52">
@@ -3521,7 +2837,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3530,7 +2846,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12680.3</v>
+        <v>7760.9</v>
       </c>
     </row>
     <row r="53">
@@ -3541,7 +2857,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>T027</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3550,7 +2866,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26123.5</v>
+        <v>2499.9</v>
       </c>
     </row>
     <row r="54">
@@ -3561,7 +2877,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3570,7 +2886,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>23886.1</v>
+        <v>2499.9</v>
       </c>
     </row>
     <row r="55">
@@ -3581,7 +2897,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3590,7 +2906,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>23886.1</v>
+        <v>12805.3</v>
       </c>
     </row>
     <row r="56">
@@ -3601,7 +2917,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3610,7 +2926,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>20146.8</v>
+        <v>7843.4</v>
       </c>
     </row>
     <row r="57">
@@ -3621,7 +2937,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3630,7 +2946,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10984.9</v>
+        <v>7843.4</v>
       </c>
     </row>
     <row r="58">
@@ -3641,7 +2957,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T034</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3650,7 +2966,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>32984.7</v>
+        <v>5439.5</v>
       </c>
     </row>
     <row r="59">
@@ -3661,7 +2977,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T034</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3670,7 +2986,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>32984.7</v>
+        <v>5439.5</v>
       </c>
     </row>
     <row r="60">
@@ -3681,7 +2997,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3690,7 +3006,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13689.7</v>
+        <v>7843.4</v>
       </c>
     </row>
     <row r="61">
@@ -3701,7 +3017,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3710,7 +3026,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5007</v>
+        <v>17401.2</v>
       </c>
     </row>
     <row r="62">
@@ -3721,7 +3037,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3730,7 +3046,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5007</v>
+        <v>10014.4</v>
       </c>
     </row>
     <row r="63">
@@ -3741,7 +3057,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3750,7 +3066,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9157.9</v>
+        <v>10014.4</v>
       </c>
     </row>
     <row r="64">
@@ -3761,7 +3077,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T027</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3770,7 +3086,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>25306.3</v>
+        <v>15896.3</v>
       </c>
     </row>
     <row r="65">
@@ -3781,7 +3097,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>T031</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3790,7 +3106,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>29803.9</v>
+        <v>15896.3</v>
       </c>
     </row>
     <row r="66">
@@ -3801,7 +3117,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T031</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3810,7 +3126,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>29803.9</v>
+        <v>15896.3</v>
       </c>
     </row>
     <row r="67">
@@ -3830,7 +3146,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4441.8</v>
+        <v>7222.2</v>
       </c>
     </row>
     <row r="68">
@@ -3841,7 +3157,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>T034</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3850,7 +3166,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>32298.6</v>
+        <v>7222.2</v>
       </c>
     </row>
     <row r="69">
@@ -3861,7 +3177,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3870,7 +3186,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5886.8</v>
+        <v>4011.1</v>
       </c>
     </row>
     <row r="70">
@@ -3881,7 +3197,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T028</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3890,7 +3206,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>25958.8</v>
+        <v>16892.1</v>
       </c>
     </row>
     <row r="71">
@@ -3901,7 +3217,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>T035</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3910,7 +3226,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>34317.3</v>
+        <v>15691.9</v>
       </c>
     </row>
     <row r="72">
@@ -3921,7 +3237,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>T033</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3930,7 +3246,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>32010.5</v>
+        <v>15691.9</v>
       </c>
     </row>
     <row r="73">
@@ -3941,7 +3257,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>T028</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3950,7 +3266,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25496.9</v>
+        <v>16372.8</v>
       </c>
     </row>
     <row r="74">
@@ -3961,7 +3277,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>T035</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3970,7 +3286,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>34774.5</v>
+        <v>16372.8</v>
       </c>
     </row>
     <row r="75">
@@ -3981,7 +3297,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>T033</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3990,7 +3306,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>31548.6</v>
+        <v>15136.5</v>
       </c>
     </row>
     <row r="76">
@@ -4001,7 +3317,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4010,7 +3326,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7060.3</v>
+        <v>2830.9</v>
       </c>
     </row>
     <row r="77">
@@ -4021,7 +3337,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>T032</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4030,7 +3346,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30716</v>
+        <v>2830.9</v>
       </c>
     </row>
     <row r="78">
@@ -4041,7 +3357,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>T032</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4050,7 +3366,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30716</v>
+        <v>2830.9</v>
       </c>
     </row>
     <row r="79">
@@ -4061,7 +3377,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4070,7 +3386,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8713.200000000001</v>
+        <v>4735.7</v>
       </c>
     </row>
     <row r="80">
@@ -4081,7 +3397,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>T030</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4090,7 +3406,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28929.6</v>
+        <v>4735.7</v>
       </c>
     </row>
     <row r="81">
@@ -4101,7 +3417,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4110,7 +3426,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6467.2</v>
+        <v>4735.7</v>
       </c>
     </row>
   </sheetData>
@@ -4124,7 +3440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4217,25 +3533,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>109.2388</v>
+        <v>109.215383</v>
       </c>
       <c r="F2" t="n">
-        <v>23.006658</v>
+        <v>23.028329</v>
       </c>
       <c r="G2" t="n">
-        <v>440.6</v>
+        <v>562.1</v>
       </c>
       <c r="H2" t="n">
-        <v>298.4</v>
+        <v>452.7</v>
       </c>
       <c r="I2" t="n">
-        <v>5072</v>
+        <v>3051.2</v>
       </c>
       <c r="J2" t="n">
-        <v>5171.2</v>
+        <v>3314.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4001</v>
+        <v>0.5446</v>
       </c>
     </row>
     <row r="3">
@@ -4258,25 +3574,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>109.230994</v>
+        <v>109.266119</v>
       </c>
       <c r="F3" t="n">
         <v>23.010269</v>
       </c>
       <c r="G3" t="n">
-        <v>395.2</v>
+        <v>559</v>
       </c>
       <c r="H3" t="n">
-        <v>239.9</v>
+        <v>525.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5474.1</v>
+        <v>3515.3</v>
       </c>
       <c r="J3" t="n">
-        <v>5509.7</v>
+        <v>3855.4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4687</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="4">
@@ -4296,28 +3612,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5171.2</v>
+        <v>3314.7</v>
       </c>
       <c r="E4" t="n">
-        <v>109.219286</v>
+        <v>109.207577</v>
       </c>
       <c r="F4" t="n">
-        <v>23.006658</v>
+        <v>23.028329</v>
       </c>
       <c r="G4" t="n">
-        <v>460.5</v>
+        <v>599.6</v>
       </c>
       <c r="H4" t="n">
-        <v>5499.5</v>
+        <v>3812</v>
       </c>
       <c r="I4" t="n">
-        <v>7075.5</v>
+        <v>5972.6</v>
       </c>
       <c r="J4" t="n">
-        <v>7206.4</v>
+        <v>6283.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5463</v>
+        <v>0.8236</v>
       </c>
     </row>
     <row r="5">
@@ -4337,28 +3653,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5509.7</v>
+        <v>3855.4</v>
       </c>
       <c r="E5" t="n">
-        <v>109.266119</v>
+        <v>109.242702</v>
       </c>
       <c r="F5" t="n">
-        <v>23.010269</v>
+        <v>23.060836</v>
       </c>
       <c r="G5" t="n">
-        <v>559</v>
+        <v>555.5</v>
       </c>
       <c r="H5" t="n">
-        <v>6035.1</v>
+        <v>4527</v>
       </c>
       <c r="I5" t="n">
-        <v>7683.3</v>
+        <v>6136.3</v>
       </c>
       <c r="J5" t="n">
-        <v>8023.4</v>
+        <v>6620.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6842</v>
+        <v>0.7677</v>
       </c>
     </row>
     <row r="6">
@@ -4378,28 +3694,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7206.4</v>
+        <v>6283.7</v>
       </c>
       <c r="E6" t="n">
-        <v>109.207577</v>
+        <v>109.203674</v>
       </c>
       <c r="F6" t="n">
-        <v>23.028329</v>
+        <v>23.039165</v>
       </c>
       <c r="G6" t="n">
-        <v>599.6</v>
+        <v>705.6</v>
       </c>
       <c r="H6" t="n">
-        <v>7703.8</v>
+        <v>6880.9</v>
       </c>
       <c r="I6" t="n">
-        <v>9321.5</v>
+        <v>8540.299999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>9632.6</v>
+        <v>8959</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6577</v>
+        <v>0.7277</v>
       </c>
     </row>
     <row r="7">
@@ -4419,28 +3735,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8023.4</v>
+        <v>6620.2</v>
       </c>
       <c r="E7" t="n">
-        <v>109.2388</v>
+        <v>109.203674</v>
       </c>
       <c r="F7" t="n">
-        <v>23.006658</v>
+        <v>23.021105</v>
       </c>
       <c r="G7" t="n">
-        <v>440.6</v>
+        <v>614</v>
       </c>
       <c r="H7" t="n">
-        <v>8321.799999999999</v>
+        <v>7109.6</v>
       </c>
       <c r="I7" t="n">
-        <v>9625</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>9724.200000000001</v>
+        <v>9811.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4455</v>
+        <v>0.8911</v>
       </c>
     </row>
     <row r="8">
@@ -4460,28 +3776,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9632.6</v>
+        <v>8959</v>
       </c>
       <c r="E8" t="n">
-        <v>109.242702</v>
+        <v>109.2388</v>
       </c>
       <c r="F8" t="n">
-        <v>23.060836</v>
+        <v>23.006658</v>
       </c>
       <c r="G8" t="n">
-        <v>555.5</v>
+        <v>440.6</v>
       </c>
       <c r="H8" t="n">
-        <v>10304.1</v>
+        <v>9257.4</v>
       </c>
       <c r="I8" t="n">
-        <v>11651.4</v>
+        <v>11081.8</v>
       </c>
       <c r="J8" t="n">
-        <v>12135.3</v>
+        <v>11181</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6876</v>
+        <v>0.6047</v>
       </c>
     </row>
     <row r="9">
@@ -4501,28 +3817,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9724.200000000001</v>
+        <v>9811.6</v>
       </c>
       <c r="E9" t="n">
-        <v>109.203674</v>
+        <v>109.234897</v>
       </c>
       <c r="F9" t="n">
-        <v>23.024717</v>
+        <v>23.060836</v>
       </c>
       <c r="G9" t="n">
-        <v>663.2</v>
+        <v>552.3</v>
       </c>
       <c r="H9" t="n">
-        <v>10239.1</v>
+        <v>10469.5</v>
       </c>
       <c r="I9" t="n">
-        <v>12187.1</v>
+        <v>12071.9</v>
       </c>
       <c r="J9" t="n">
-        <v>12519.8</v>
+        <v>12540.1</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7662</v>
+        <v>0.7586000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -4542,28 +3858,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12135.3</v>
+        <v>11181</v>
       </c>
       <c r="E10" t="n">
-        <v>109.219286</v>
+        <v>109.207577</v>
       </c>
       <c r="F10" t="n">
-        <v>23.035553</v>
+        <v>23.021105</v>
       </c>
       <c r="G10" t="n">
-        <v>494.8</v>
+        <v>541.6</v>
       </c>
       <c r="H10" t="n">
-        <v>12601.8</v>
+        <v>11631.2</v>
       </c>
       <c r="I10" t="n">
-        <v>14136.2</v>
+        <v>14078.3</v>
       </c>
       <c r="J10" t="n">
-        <v>14406.6</v>
+        <v>14337.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6209</v>
+        <v>0.8854</v>
       </c>
     </row>
     <row r="11">
@@ -4583,28 +3899,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12519.8</v>
+        <v>12540.1</v>
       </c>
       <c r="E11" t="n">
-        <v>109.203674</v>
+        <v>109.219286</v>
       </c>
       <c r="F11" t="n">
-        <v>23.039165</v>
+        <v>23.035553</v>
       </c>
       <c r="G11" t="n">
-        <v>705.6</v>
+        <v>494.8</v>
       </c>
       <c r="H11" t="n">
-        <v>13117.1</v>
+        <v>13006.6</v>
       </c>
       <c r="I11" t="n">
-        <v>14356.2</v>
+        <v>14435</v>
       </c>
       <c r="J11" t="n">
-        <v>14775</v>
+        <v>14705.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5885</v>
       </c>
     </row>
     <row r="12">
@@ -4624,28 +3940,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14406.6</v>
+        <v>14337.2</v>
       </c>
       <c r="E12" t="n">
-        <v>109.203674</v>
+        <v>109.262217</v>
       </c>
       <c r="F12" t="n">
         <v>23.017493</v>
       </c>
       <c r="G12" t="n">
-        <v>653.1</v>
+        <v>572.1</v>
       </c>
       <c r="H12" t="n">
-        <v>14895.2</v>
+        <v>14837.7</v>
       </c>
       <c r="I12" t="n">
-        <v>16455.2</v>
+        <v>16380.8</v>
       </c>
       <c r="J12" t="n">
-        <v>16760.9</v>
+        <v>16693.4</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="13">
@@ -4665,28 +3981,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14775</v>
+        <v>14705.5</v>
       </c>
       <c r="E13" t="n">
-        <v>109.234897</v>
+        <v>109.273925</v>
       </c>
       <c r="F13" t="n">
-        <v>23.060836</v>
+        <v>23.039165</v>
       </c>
       <c r="G13" t="n">
-        <v>552.3</v>
+        <v>597.1</v>
       </c>
       <c r="H13" t="n">
-        <v>15432.9</v>
+        <v>15354.1</v>
       </c>
       <c r="I13" t="n">
-        <v>16278.3</v>
+        <v>17888.9</v>
       </c>
       <c r="J13" t="n">
-        <v>16746.4</v>
+        <v>18350</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5273</v>
+        <v>1.0357</v>
       </c>
     </row>
     <row r="14">
@@ -4697,7 +4013,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4706,28 +4022,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16746.4</v>
+        <v>16693.4</v>
       </c>
       <c r="E14" t="n">
         <v>109.219286</v>
       </c>
       <c r="F14" t="n">
-        <v>23.017493</v>
+        <v>23.035553</v>
       </c>
       <c r="G14" t="n">
-        <v>511.8</v>
+        <v>494.8</v>
       </c>
       <c r="H14" t="n">
-        <v>17112.7</v>
+        <v>17159.9</v>
       </c>
       <c r="I14" t="n">
-        <v>18286.7</v>
+        <v>18934.8</v>
       </c>
       <c r="J14" t="n">
-        <v>18460.6</v>
+        <v>19205.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4435</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="15">
@@ -4738,7 +4054,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4747,684 +4063,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16760.9</v>
+        <v>18350</v>
       </c>
       <c r="E15" t="n">
-        <v>109.219286</v>
+        <v>109.203674</v>
       </c>
       <c r="F15" t="n">
-        <v>23.035553</v>
+        <v>23.017493</v>
       </c>
       <c r="G15" t="n">
-        <v>494.8</v>
+        <v>653.1</v>
       </c>
       <c r="H15" t="n">
-        <v>17227.4</v>
+        <v>18838.6</v>
       </c>
       <c r="I15" t="n">
-        <v>18423.4</v>
+        <v>20610.4</v>
       </c>
       <c r="J15" t="n">
-        <v>18693.8</v>
+        <v>20916.1</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5175</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>RT15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>R-P03</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>18460.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F16" t="n">
-        <v>23.035553</v>
-      </c>
-      <c r="G16" t="n">
-        <v>494.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>18927.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>20040.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>20311</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.4923</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>RT16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>R-P04</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>18693.8</v>
-      </c>
-      <c r="E17" t="n">
-        <v>109.242702</v>
-      </c>
-      <c r="F17" t="n">
-        <v>23.060836</v>
-      </c>
-      <c r="G17" t="n">
-        <v>555.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>19365.3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>20813.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>21297.1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.7184</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>RT17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>R-P06</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>20311</v>
-      </c>
-      <c r="E18" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F18" t="n">
-        <v>23.017493</v>
-      </c>
-      <c r="G18" t="n">
-        <v>511.8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>20677.3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>22285.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>22459.1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.5760999999999999</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>RT18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>R-P05</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>21297.1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F19" t="n">
-        <v>23.035553</v>
-      </c>
-      <c r="G19" t="n">
-        <v>494.8</v>
-      </c>
-      <c r="H19" t="n">
-        <v>21763.7</v>
-      </c>
-      <c r="I19" t="n">
-        <v>22781.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>23051.9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.463</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>RT19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>R-P01</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>22459.1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F20" t="n">
-        <v>23.035553</v>
-      </c>
-      <c r="G20" t="n">
-        <v>494.8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>22925.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>24313.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>24583.7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.5760999999999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RT20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>R-P02</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>23051.9</v>
-      </c>
-      <c r="E21" t="n">
-        <v>109.215383</v>
-      </c>
-      <c r="F21" t="n">
-        <v>23.028329</v>
-      </c>
-      <c r="G21" t="n">
-        <v>562.1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>23504.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>24389.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>24653.1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.4079</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RT21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>R-P03</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>24583.7</v>
-      </c>
-      <c r="E22" t="n">
-        <v>109.273925</v>
-      </c>
-      <c r="F22" t="n">
-        <v>23.031941</v>
-      </c>
-      <c r="G22" t="n">
-        <v>562.3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>25203.5</v>
-      </c>
-      <c r="I22" t="n">
-        <v>27054.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>27486.8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>RT22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>R-P04</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>24653.1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F23" t="n">
-        <v>23.039165</v>
-      </c>
-      <c r="G23" t="n">
-        <v>528.6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>25153</v>
-      </c>
-      <c r="I23" t="n">
-        <v>26212.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>26519.3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.4948</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>RT23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>R-P06</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>26519.3</v>
-      </c>
-      <c r="E24" t="n">
-        <v>109.242702</v>
-      </c>
-      <c r="F24" t="n">
-        <v>23.006658</v>
-      </c>
-      <c r="G24" t="n">
-        <v>504.3</v>
-      </c>
-      <c r="H24" t="n">
-        <v>26855.6</v>
-      </c>
-      <c r="I24" t="n">
-        <v>26855.6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>26996.6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.0682</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RT24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>R-P05</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>26996.6</v>
-      </c>
-      <c r="E25" t="n">
-        <v>109.234897</v>
-      </c>
-      <c r="F25" t="n">
-        <v>23.060836</v>
-      </c>
-      <c r="G25" t="n">
-        <v>552.3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>27654.6</v>
-      </c>
-      <c r="I25" t="n">
-        <v>28780.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>29249</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.6132</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RT25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>R-P01</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>27486.8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>109.195869</v>
-      </c>
-      <c r="F26" t="n">
-        <v>23.021105</v>
-      </c>
-      <c r="G26" t="n">
-        <v>739.9</v>
-      </c>
-      <c r="H26" t="n">
-        <v>28061</v>
-      </c>
-      <c r="I26" t="n">
-        <v>29537.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>29938</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.6535</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RT26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>R-P02</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>29249</v>
-      </c>
-      <c r="E27" t="n">
-        <v>109.242702</v>
-      </c>
-      <c r="F27" t="n">
-        <v>23.006658</v>
-      </c>
-      <c r="G27" t="n">
-        <v>504.3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>29585.3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>30271.8</v>
-      </c>
-      <c r="J27" t="n">
-        <v>30412.8</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.2779</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>RT27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>R-P06</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>29938</v>
-      </c>
-      <c r="E28" t="n">
-        <v>109.266119</v>
-      </c>
-      <c r="F28" t="n">
-        <v>23.010269</v>
-      </c>
-      <c r="G28" t="n">
-        <v>559</v>
-      </c>
-      <c r="H28" t="n">
-        <v>30463.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>31339</v>
-      </c>
-      <c r="J28" t="n">
-        <v>31679.1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.4481</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RT28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>R-P04</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>30412.8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>109.262217</v>
-      </c>
-      <c r="F29" t="n">
-        <v>23.017493</v>
-      </c>
-      <c r="G29" t="n">
-        <v>572.1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>30913.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>32662</v>
-      </c>
-      <c r="J29" t="n">
-        <v>32974.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.6934</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RT29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>R-P03</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>31679.1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>109.203674</v>
-      </c>
-      <c r="F30" t="n">
-        <v>23.039165</v>
-      </c>
-      <c r="G30" t="n">
-        <v>705.6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>32276.3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>33651.2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>34070</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.6408</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>RT30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>R-P05</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>32974.6</v>
-      </c>
-      <c r="E31" t="n">
-        <v>109.273925</v>
-      </c>
-      <c r="F31" t="n">
-        <v>23.031941</v>
-      </c>
-      <c r="G31" t="n">
-        <v>562.3</v>
-      </c>
-      <c r="H31" t="n">
-        <v>33594.4</v>
-      </c>
-      <c r="I31" t="n">
-        <v>35219.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>35651.9</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.739</v>
+        <v>0.6963</v>
       </c>
     </row>
   </sheetData>
@@ -5438,7 +4098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5484,7 +4144,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5493,10 +4153,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>298.4</v>
+        <v>452.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5072</v>
+        <v>3051.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -5512,7 +4172,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5521,10 +4181,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>239.9</v>
+        <v>525.4</v>
       </c>
       <c r="D3" t="n">
-        <v>5474.1</v>
+        <v>3515.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -5540,7 +4200,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5549,10 +4209,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5499.5</v>
+        <v>3812</v>
       </c>
       <c r="D4" t="n">
-        <v>7075.5</v>
+        <v>5972.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -5568,7 +4228,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5577,10 +4237,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6035.1</v>
+        <v>4527</v>
       </c>
       <c r="D5" t="n">
-        <v>7683.3</v>
+        <v>6136.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -5596,7 +4256,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5605,10 +4265,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7703.8</v>
+        <v>6880.9</v>
       </c>
       <c r="D6" t="n">
-        <v>9321.5</v>
+        <v>8540.299999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -5624,7 +4284,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5633,10 +4293,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8321.799999999999</v>
+        <v>7109.6</v>
       </c>
       <c r="D7" t="n">
-        <v>9625</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5652,7 +4312,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5661,10 +4321,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10304.1</v>
+        <v>9257.4</v>
       </c>
       <c r="D8" t="n">
-        <v>11651.4</v>
+        <v>11081.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5680,7 +4340,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5689,10 +4349,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10239.1</v>
+        <v>10469.5</v>
       </c>
       <c r="D9" t="n">
-        <v>12187.1</v>
+        <v>12071.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5708,7 +4368,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5717,10 +4377,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12601.8</v>
+        <v>11631.2</v>
       </c>
       <c r="D10" t="n">
-        <v>14136.2</v>
+        <v>14078.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5736,7 +4396,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5745,10 +4405,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13117.1</v>
+        <v>13006.6</v>
       </c>
       <c r="D11" t="n">
-        <v>14356.2</v>
+        <v>14435</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -5764,7 +4424,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5773,10 +4433,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14895.2</v>
+        <v>14837.7</v>
       </c>
       <c r="D12" t="n">
-        <v>16455.2</v>
+        <v>16380.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -5792,7 +4452,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5801,10 +4461,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15432.9</v>
+        <v>15354.1</v>
       </c>
       <c r="D13" t="n">
-        <v>16278.3</v>
+        <v>17888.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -5820,7 +4480,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5829,10 +4489,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17112.7</v>
+        <v>17159.9</v>
       </c>
       <c r="D14" t="n">
-        <v>18286.7</v>
+        <v>18934.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -5848,7 +4508,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5857,10 +4517,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17227.4</v>
+        <v>18838.6</v>
       </c>
       <c r="D15" t="n">
-        <v>18423.4</v>
+        <v>20610.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -5870,454 +4530,6 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>RT14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>T021</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>18927.1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>20040.6</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>RT15</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>T022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>19365.3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>20813.3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>RT16</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>20677.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>22285.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>RT17</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>21763.7</v>
-      </c>
-      <c r="D19" t="n">
-        <v>22781.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>RT18</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>22925.6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>24313.3</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>RT19</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>23504.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>24389.6</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>RT20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>T028</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>25203.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>27054.3</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>RT21</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>T027</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>25153</v>
-      </c>
-      <c r="D23" t="n">
-        <v>26212.6</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>RT22</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>T027</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>26855.6</v>
-      </c>
-      <c r="D24" t="n">
-        <v>26855.6</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>RT23</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>T029</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>27654.6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>28780.8</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>RT24</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>T030</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>28061</v>
-      </c>
-      <c r="D26" t="n">
-        <v>29537.9</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>RT25</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>T031</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>29585.3</v>
-      </c>
-      <c r="D27" t="n">
-        <v>30271.8</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>RT26</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>T032</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>30463.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>31339</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>RT27</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>T033</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>30913.4</v>
-      </c>
-      <c r="D29" t="n">
-        <v>32662</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>RT28</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>T034</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>32276.3</v>
-      </c>
-      <c r="D30" t="n">
-        <v>33651.2</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>RT29</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>T035</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>33594.4</v>
-      </c>
-      <c r="D31" t="n">
-        <v>35219.3</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>RT30</t>
         </is>
       </c>
     </row>
@@ -6423,19 +4635,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -6462,19 +4674,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -6501,19 +4713,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -6533,32 +4745,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S001|S002|S003|S004|S005|S007|S008|S009|S010|S011|S012|S013|S015</t>
+          <t>S001|S002|S004|S005|S008|S009|S010|S012|S013</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6572,32 +4784,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S003|S006|S007|S011</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -6618,19 +4830,19 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>

--- a/otheragent/results/结果提交文件.xlsx
+++ b/otheragent/results/结果提交文件.xlsx
@@ -1156,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1164,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -1237,14 +1237,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S001→S009→S002</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1490.7</v>
+        <v>2683.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.27999</v>
+        <v>5.75837</v>
       </c>
     </row>
     <row r="3">
@@ -1273,14 +1273,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S001→S002</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1358.7</v>
+        <v>2297.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.30807</v>
+        <v>5.61535</v>
       </c>
     </row>
     <row r="4">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C-B03</t>
+          <t>B-B01</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1358.7</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S013→S012</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3051.2</v>
+        <v>2143.3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.03178</v>
+        <v>2.68289</v>
       </c>
     </row>
     <row r="5">
@@ -1327,32 +1327,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C-B04</t>
+          <t>B-B02</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1490.7</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S001→S012</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3515.3</v>
+        <v>2115.1</v>
       </c>
       <c r="H5" t="n">
-        <v>3.73421</v>
+        <v>2.55544</v>
       </c>
     </row>
     <row r="6">
@@ -1363,32 +1363,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C-B01</t>
+          <t>A-B01</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3051.2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S011→S015→S005</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5972.6</v>
+        <v>1713.5</v>
       </c>
       <c r="H6" t="n">
-        <v>5.42523</v>
+        <v>1.89948</v>
       </c>
     </row>
     <row r="7">
@@ -1399,32 +1399,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C-B02</t>
+          <t>A-B02</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3515.3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S004→S008</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6136.3</v>
+        <v>1650.4</v>
       </c>
       <c r="H7" t="n">
-        <v>6.30729</v>
+        <v>1.89044</v>
       </c>
     </row>
     <row r="8">
@@ -1435,32 +1435,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C-B03</t>
+          <t>A-B03</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5972.6</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S005→S008</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8540.299999999999</v>
+        <v>1606.4</v>
       </c>
       <c r="H8" t="n">
-        <v>6.37084</v>
+        <v>1.89322</v>
       </c>
     </row>
     <row r="9">
@@ -1471,32 +1471,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C-B04</t>
+          <t>A-B04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6136.3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S011→S007→S003→S006</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9508.200000000001</v>
+        <v>1653.5</v>
       </c>
       <c r="H9" t="n">
-        <v>6.31517</v>
+        <v>1.8668</v>
       </c>
     </row>
     <row r="10">
@@ -1507,32 +1507,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C-B01</t>
+          <t>A-B05</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8540.299999999999</v>
+        <v>1606.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S001→S009→S005</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>11081.8</v>
+        <v>3196.9</v>
       </c>
       <c r="H10" t="n">
-        <v>4.88214</v>
+        <v>1.91929</v>
       </c>
     </row>
     <row r="11">
@@ -1543,32 +1543,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C-B02</t>
+          <t>A-B06</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9508.200000000001</v>
+        <v>1650.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S004→S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12071.9</v>
+        <v>2958.5</v>
       </c>
       <c r="H11" t="n">
-        <v>6.31965</v>
+        <v>1.26313</v>
       </c>
     </row>
     <row r="12">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C-B03</t>
+          <t>B-B03</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11099</v>
+        <v>2115.1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S006→S007→S003</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>14078.3</v>
+        <v>3976.2</v>
       </c>
       <c r="H12" t="n">
-        <v>6.3727</v>
+        <v>2.13643</v>
       </c>
     </row>
     <row r="13">
@@ -1615,32 +1615,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C-B04</t>
+          <t>B-B04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12071.9</v>
+        <v>2143.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S001→S002</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>14435</v>
+        <v>3348.2</v>
       </c>
       <c r="H13" t="n">
-        <v>6.02199</v>
+        <v>1.2923</v>
       </c>
     </row>
     <row r="14">
@@ -1661,22 +1661,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C-B01</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14078.3</v>
+        <v>2297.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S013→S012</t>
+          <t>S001→S009</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>16380.8</v>
+        <v>4397</v>
       </c>
       <c r="H14" t="n">
-        <v>5.08164</v>
+        <v>4.2936</v>
       </c>
     </row>
     <row r="15">
@@ -1687,32 +1687,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C-B02</t>
+          <t>A-B03</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14616.8</v>
+        <v>2653.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S010→S013→S012→S009</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>17888.9</v>
+        <v>3964.4</v>
       </c>
       <c r="H15" t="n">
-        <v>6.39574</v>
+        <v>1.31031</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1733,22 +1733,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C-B03</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>16637.6</v>
+        <v>2683.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S001→S002</t>
+          <t>S011→S015→S007</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>18934.8</v>
+        <v>5370.2</v>
       </c>
       <c r="H16" t="n">
-        <v>5.12056</v>
+        <v>4.52496</v>
       </c>
     </row>
     <row r="17">
@@ -1759,32 +1759,464 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A-B04</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2692.8</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S005→S008</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5120.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.33864</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A-B01</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2958.5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>5209</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.9768</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A-B02</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3196.9</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>5376</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.08691</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B-B02</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3889.1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>5811.1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.03546</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A-B06</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3964.4</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>6127.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.0712</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B-B01</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3976.2</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>5730</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.40615</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C-B02</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4651.3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S006→S003→S007</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>7689.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.39125</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A-B03</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5120.4</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>7283.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.3049</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A-B05</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5209</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S015</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>7172.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.46994</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>U07</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>C-B04</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>17888.9</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>S006→S003</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>20610.4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>5.3764</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C-B01</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5370.2</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S005→S004</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>7883.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.56312</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>B-B03</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5730</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>6876.3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.02534</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>B-B04</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5811.1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>7325.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.77089</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>A-B01</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6569</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>8819.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.95919</v>
       </c>
     </row>
   </sheetData>
@@ -1837,7 +2269,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1846,7 +2278,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1048.5</v>
+        <v>1066.5</v>
       </c>
     </row>
     <row r="3">
@@ -1857,7 +2289,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1866,7 +2298,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1180.5</v>
+        <v>6586.3</v>
       </c>
     </row>
     <row r="4">
@@ -1877,7 +2309,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1886,7 +2318,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13072.4</v>
+        <v>6586.3</v>
       </c>
     </row>
     <row r="5">
@@ -1897,7 +2329,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1906,7 +2338,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1180.5</v>
+        <v>826.3</v>
       </c>
     </row>
     <row r="6">
@@ -1917,7 +2349,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1926,7 +2358,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17680.1</v>
+        <v>3405.7</v>
       </c>
     </row>
     <row r="7">
@@ -1937,7 +2369,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1946,7 +2378,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1180.5</v>
+        <v>2617.6</v>
       </c>
     </row>
     <row r="8">
@@ -1957,7 +2389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1966,7 +2398,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1180.5</v>
+        <v>2617.6</v>
       </c>
     </row>
     <row r="9">
@@ -1977,7 +2409,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1986,7 +2418,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17680.1</v>
+        <v>2617.6</v>
       </c>
     </row>
     <row r="10">
@@ -1997,7 +2429,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2006,7 +2438,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17680.1</v>
+        <v>1042.5</v>
       </c>
     </row>
     <row r="11">
@@ -2017,7 +2449,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2026,7 +2458,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9510.799999999999</v>
+        <v>3405.7</v>
       </c>
     </row>
     <row r="12">
@@ -2037,7 +2469,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2046,7 +2478,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1180.5</v>
+        <v>3405.7</v>
       </c>
     </row>
     <row r="13">
@@ -2057,7 +2489,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2066,7 +2498,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1180.5</v>
+        <v>3405.7</v>
       </c>
     </row>
     <row r="14">
@@ -2086,7 +2518,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1048.5</v>
+        <v>1042.5</v>
       </c>
     </row>
     <row r="15">
@@ -2106,7 +2538,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1048.5</v>
+        <v>1042.5</v>
       </c>
     </row>
     <row r="16">
@@ -2117,7 +2549,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2126,7 +2558,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1048.5</v>
+        <v>1066.5</v>
       </c>
     </row>
     <row r="17">
@@ -2137,7 +2569,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2146,7 +2578,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13816.3</v>
+        <v>5135</v>
       </c>
     </row>
     <row r="18">
@@ -2157,7 +2589,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2166,7 +2598,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13816.3</v>
+        <v>5135</v>
       </c>
     </row>
     <row r="19">
@@ -2177,7 +2609,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2186,7 +2618,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11453.1</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="20">
@@ -2197,7 +2629,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2206,7 +2638,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18316</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="21">
@@ -2217,7 +2649,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2226,7 +2658,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18316</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="22">
@@ -2237,7 +2669,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2246,7 +2678,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13816.3</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="23">
@@ -2257,7 +2689,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2266,7 +2698,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13816.3</v>
+        <v>1678.4</v>
       </c>
     </row>
     <row r="24">
@@ -2277,7 +2709,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2286,7 +2718,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13816.3</v>
+        <v>1678.4</v>
       </c>
     </row>
     <row r="25">
@@ -2297,7 +2729,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T028</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2306,7 +2738,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8322.799999999999</v>
+        <v>7972.2</v>
       </c>
     </row>
     <row r="26">
@@ -2317,7 +2749,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T028</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2326,7 +2758,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8322.799999999999</v>
+        <v>7972.2</v>
       </c>
     </row>
     <row r="27">
@@ -2337,7 +2769,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2346,7 +2778,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8322.799999999999</v>
+        <v>6685.6</v>
       </c>
     </row>
     <row r="28">
@@ -2357,7 +2789,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2366,7 +2798,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19827.2</v>
+        <v>4361.7</v>
       </c>
     </row>
     <row r="29">
@@ -2377,7 +2809,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2386,7 +2818,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>19827.2</v>
+        <v>4361.7</v>
       </c>
     </row>
     <row r="30">
@@ -2397,7 +2829,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2406,7 +2838,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13295.2</v>
+        <v>6685.6</v>
       </c>
     </row>
     <row r="31">
@@ -2417,7 +2849,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2426,7 +2858,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13295.2</v>
+        <v>6685.6</v>
       </c>
     </row>
     <row r="32">
@@ -2437,7 +2869,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2446,7 +2878,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8322.799999999999</v>
+        <v>6685.6</v>
       </c>
     </row>
     <row r="33">
@@ -2457,7 +2889,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2466,7 +2898,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10989.9</v>
+        <v>7165.6</v>
       </c>
     </row>
     <row r="34">
@@ -2477,7 +2909,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2486,7 +2918,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10989.9</v>
+        <v>7165.6</v>
       </c>
     </row>
     <row r="35">
@@ -2497,7 +2929,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2506,7 +2938,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4895.1</v>
+        <v>4568.1</v>
       </c>
     </row>
     <row r="36">
@@ -2517,7 +2949,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2526,7 +2958,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4895.1</v>
+        <v>4568.1</v>
       </c>
     </row>
     <row r="37">
@@ -2537,7 +2969,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2546,7 +2978,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10989.9</v>
+        <v>5131.8</v>
       </c>
     </row>
     <row r="38">
@@ -2557,7 +2989,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2566,7 +2998,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10989.9</v>
+        <v>5131.8</v>
       </c>
     </row>
     <row r="39">
@@ -2577,7 +3009,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2586,7 +3018,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7236.9</v>
+        <v>3790.9</v>
       </c>
     </row>
     <row r="40">
@@ -2597,7 +3029,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2606,7 +3038,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5469.6</v>
+        <v>6604.4</v>
       </c>
     </row>
     <row r="41">
@@ -2617,7 +3049,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T027</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2626,7 +3058,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10578.8</v>
+        <v>6851.2</v>
       </c>
     </row>
     <row r="42">
@@ -2637,7 +3069,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T027</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2646,7 +3078,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10578.8</v>
+        <v>6851.2</v>
       </c>
     </row>
     <row r="43">
@@ -2657,7 +3089,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2666,7 +3098,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7236.9</v>
+        <v>6604.4</v>
       </c>
     </row>
     <row r="44">
@@ -2677,7 +3109,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2686,7 +3118,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7236.9</v>
+        <v>6604.4</v>
       </c>
     </row>
     <row r="45">
@@ -2697,7 +3129,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2706,7 +3138,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12163</v>
+        <v>5745.3</v>
       </c>
     </row>
     <row r="46">
@@ -2717,7 +3149,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2726,7 +3158,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9157.5</v>
+        <v>5745.3</v>
       </c>
     </row>
     <row r="47">
@@ -2737,7 +3169,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2746,7 +3178,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>18958.9</v>
+        <v>3587.6</v>
       </c>
     </row>
     <row r="48">
@@ -2757,7 +3189,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2766,7 +3198,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18958.9</v>
+        <v>3587.6</v>
       </c>
     </row>
     <row r="49">
@@ -2777,7 +3209,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2786,7 +3218,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>18958.9</v>
+        <v>3024.5</v>
       </c>
     </row>
     <row r="50">
@@ -2797,7 +3229,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2806,7 +3238,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12163</v>
+        <v>3024.5</v>
       </c>
     </row>
     <row r="51">
@@ -2817,7 +3249,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2826,7 +3258,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12805.3</v>
+        <v>4818.9</v>
       </c>
     </row>
     <row r="52">
@@ -2837,7 +3269,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2846,7 +3278,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7760.9</v>
+        <v>7138.5</v>
       </c>
     </row>
     <row r="53">
@@ -2857,7 +3289,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2866,7 +3298,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2499.9</v>
+        <v>1134.4</v>
       </c>
     </row>
     <row r="54">
@@ -2877,7 +3309,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2886,7 +3318,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2499.9</v>
+        <v>1134.4</v>
       </c>
     </row>
     <row r="55">
@@ -2897,7 +3329,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2906,7 +3338,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12805.3</v>
+        <v>1074.4</v>
       </c>
     </row>
     <row r="56">
@@ -2917,7 +3349,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T023</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2926,7 +3358,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>7843.4</v>
+        <v>6482</v>
       </c>
     </row>
     <row r="57">
@@ -2937,7 +3369,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2946,7 +3378,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>7843.4</v>
+        <v>5326</v>
       </c>
     </row>
     <row r="58">
@@ -2957,7 +3389,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2966,7 +3398,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5439.5</v>
+        <v>5326</v>
       </c>
     </row>
     <row r="59">
@@ -2977,7 +3409,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2986,7 +3418,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5439.5</v>
+        <v>4319.2</v>
       </c>
     </row>
     <row r="60">
@@ -2997,7 +3429,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T023</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3006,7 +3438,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7843.4</v>
+        <v>6482</v>
       </c>
     </row>
     <row r="61">
@@ -3017,7 +3449,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3026,7 +3458,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>17401.2</v>
+        <v>1534.2</v>
       </c>
     </row>
     <row r="62">
@@ -3037,7 +3469,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3046,7 +3478,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10014.4</v>
+        <v>3909.3</v>
       </c>
     </row>
     <row r="63">
@@ -3057,7 +3489,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3066,7 +3498,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10014.4</v>
+        <v>3909.3</v>
       </c>
     </row>
     <row r="64">
@@ -3077,7 +3509,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3086,7 +3518,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15896.3</v>
+        <v>1102.8</v>
       </c>
     </row>
     <row r="65">
@@ -3097,7 +3529,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3106,7 +3538,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15896.3</v>
+        <v>1102.8</v>
       </c>
     </row>
     <row r="66">
@@ -3117,7 +3549,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3126,7 +3558,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15896.3</v>
+        <v>2649.2</v>
       </c>
     </row>
     <row r="67">
@@ -3137,7 +3569,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3146,7 +3578,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>7222.2</v>
+        <v>3715.6</v>
       </c>
     </row>
     <row r="68">
@@ -3157,7 +3589,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3166,7 +3598,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7222.2</v>
+        <v>3715.6</v>
       </c>
     </row>
     <row r="69">
@@ -3177,7 +3609,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3186,7 +3618,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4011.1</v>
+        <v>3715.6</v>
       </c>
     </row>
     <row r="70">
@@ -3197,7 +3629,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3206,7 +3638,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>16892.1</v>
+        <v>1491.8</v>
       </c>
     </row>
     <row r="71">
@@ -3217,7 +3649,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3226,7 +3658,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>15691.9</v>
+        <v>1491.8</v>
       </c>
     </row>
     <row r="72">
@@ -3237,7 +3669,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3246,7 +3678,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>15691.9</v>
+        <v>1463.6</v>
       </c>
     </row>
     <row r="73">
@@ -3257,7 +3689,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3266,7 +3698,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>16372.8</v>
+        <v>1080.7</v>
       </c>
     </row>
     <row r="74">
@@ -3277,7 +3709,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3286,7 +3718,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>16372.8</v>
+        <v>1080.7</v>
       </c>
     </row>
     <row r="75">
@@ -3297,7 +3729,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3306,7 +3738,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>15136.5</v>
+        <v>999.9</v>
       </c>
     </row>
     <row r="76">
@@ -3317,7 +3749,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3326,7 +3758,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2830.9</v>
+        <v>3353.2</v>
       </c>
     </row>
     <row r="77">
@@ -3337,7 +3769,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3346,7 +3778,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2830.9</v>
+        <v>3353.2</v>
       </c>
     </row>
     <row r="78">
@@ -3357,7 +3789,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3366,7 +3798,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2830.9</v>
+        <v>3353.2</v>
       </c>
     </row>
     <row r="79">
@@ -3377,7 +3809,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3386,7 +3818,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4735.7</v>
+        <v>4368.3</v>
       </c>
     </row>
     <row r="80">
@@ -3397,7 +3829,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T024</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3406,7 +3838,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4735.7</v>
+        <v>6464.3</v>
       </c>
     </row>
     <row r="81">
@@ -3417,7 +3849,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T024</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3426,7 +3858,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4735.7</v>
+        <v>6464.3</v>
       </c>
     </row>
   </sheetData>
@@ -3440,7 +3872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3545,13 +3977,13 @@
         <v>452.7</v>
       </c>
       <c r="I2" t="n">
-        <v>3051.2</v>
+        <v>1653.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3314.7</v>
+        <v>1917</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5446</v>
+        <v>0.5044</v>
       </c>
     </row>
     <row r="3">
@@ -3574,25 +4006,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>109.266119</v>
+        <v>109.262217</v>
       </c>
       <c r="F3" t="n">
-        <v>23.010269</v>
+        <v>23.017493</v>
       </c>
       <c r="G3" t="n">
-        <v>559</v>
+        <v>572.1</v>
       </c>
       <c r="H3" t="n">
-        <v>525.4</v>
+        <v>500.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3515.3</v>
+        <v>2115.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3855.4</v>
+        <v>2427.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.68</v>
+        <v>0.6602</v>
       </c>
     </row>
     <row r="4">
@@ -3612,28 +4044,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3314.7</v>
+        <v>1917</v>
       </c>
       <c r="E4" t="n">
-        <v>109.207577</v>
+        <v>109.215383</v>
       </c>
       <c r="F4" t="n">
         <v>23.028329</v>
       </c>
       <c r="G4" t="n">
-        <v>599.6</v>
+        <v>562.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3812</v>
+        <v>2369.7</v>
       </c>
       <c r="I4" t="n">
-        <v>5972.6</v>
+        <v>2369.7</v>
       </c>
       <c r="J4" t="n">
-        <v>6283.7</v>
+        <v>2633.1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8236</v>
+        <v>0.1374</v>
       </c>
     </row>
     <row r="5">
@@ -3653,28 +4085,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3855.4</v>
+        <v>2427.7</v>
       </c>
       <c r="E5" t="n">
         <v>109.242702</v>
       </c>
       <c r="F5" t="n">
-        <v>23.060836</v>
+        <v>23.006658</v>
       </c>
       <c r="G5" t="n">
-        <v>555.5</v>
+        <v>504.3</v>
       </c>
       <c r="H5" t="n">
-        <v>4527</v>
+        <v>2764</v>
       </c>
       <c r="I5" t="n">
-        <v>6136.3</v>
+        <v>2764</v>
       </c>
       <c r="J5" t="n">
-        <v>6620.2</v>
+        <v>2905</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7677</v>
+        <v>0.0682</v>
       </c>
     </row>
     <row r="6">
@@ -3694,28 +4126,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6283.7</v>
+        <v>2633.1</v>
       </c>
       <c r="E6" t="n">
-        <v>109.203674</v>
+        <v>109.230994</v>
       </c>
       <c r="F6" t="n">
-        <v>23.039165</v>
+        <v>23.010269</v>
       </c>
       <c r="G6" t="n">
-        <v>705.6</v>
+        <v>395.2</v>
       </c>
       <c r="H6" t="n">
-        <v>6880.9</v>
+        <v>2873</v>
       </c>
       <c r="I6" t="n">
-        <v>8540.299999999999</v>
+        <v>2873</v>
       </c>
       <c r="J6" t="n">
-        <v>8959</v>
+        <v>2908.6</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7277</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="7">
@@ -3735,28 +4167,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6620.2</v>
+        <v>2905</v>
       </c>
       <c r="E7" t="n">
-        <v>109.203674</v>
+        <v>109.262217</v>
       </c>
       <c r="F7" t="n">
-        <v>23.021105</v>
+        <v>23.017493</v>
       </c>
       <c r="G7" t="n">
-        <v>614</v>
+        <v>572.1</v>
       </c>
       <c r="H7" t="n">
-        <v>7109.6</v>
+        <v>3405.5</v>
       </c>
       <c r="I7" t="n">
-        <v>9508.200000000001</v>
+        <v>3405.5</v>
       </c>
       <c r="J7" t="n">
-        <v>9811.6</v>
+        <v>3718.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8911</v>
+        <v>0.1669</v>
       </c>
     </row>
     <row r="8">
@@ -3776,28 +4208,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8959</v>
+        <v>2908.6</v>
       </c>
       <c r="E8" t="n">
-        <v>109.2388</v>
+        <v>109.219286</v>
       </c>
       <c r="F8" t="n">
-        <v>23.006658</v>
+        <v>23.035553</v>
       </c>
       <c r="G8" t="n">
-        <v>440.6</v>
+        <v>494.8</v>
       </c>
       <c r="H8" t="n">
-        <v>9257.4</v>
+        <v>3375.1</v>
       </c>
       <c r="I8" t="n">
-        <v>11081.8</v>
+        <v>3375.1</v>
       </c>
       <c r="J8" t="n">
-        <v>11181</v>
+        <v>3645.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6047</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="9">
@@ -3808,37 +4240,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>R-P02</t>
+          <t>R-P03</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9811.6</v>
+        <v>3645.5</v>
       </c>
       <c r="E9" t="n">
-        <v>109.234897</v>
+        <v>109.219286</v>
       </c>
       <c r="F9" t="n">
-        <v>23.060836</v>
+        <v>23.035553</v>
       </c>
       <c r="G9" t="n">
-        <v>552.3</v>
+        <v>494.8</v>
       </c>
       <c r="H9" t="n">
-        <v>10469.5</v>
+        <v>4112</v>
       </c>
       <c r="I9" t="n">
-        <v>12071.9</v>
+        <v>4112</v>
       </c>
       <c r="J9" t="n">
-        <v>12540.1</v>
+        <v>4382.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="10">
@@ -3849,37 +4281,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>R-P03</t>
+          <t>R-P05</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11181</v>
+        <v>3718.1</v>
       </c>
       <c r="E10" t="n">
-        <v>109.207577</v>
+        <v>109.242702</v>
       </c>
       <c r="F10" t="n">
-        <v>23.021105</v>
+        <v>23.006658</v>
       </c>
       <c r="G10" t="n">
-        <v>541.6</v>
+        <v>504.3</v>
       </c>
       <c r="H10" t="n">
-        <v>11631.2</v>
+        <v>4054.4</v>
       </c>
       <c r="I10" t="n">
-        <v>14078.3</v>
+        <v>4054.4</v>
       </c>
       <c r="J10" t="n">
-        <v>14337.2</v>
+        <v>4195.4</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8854</v>
+        <v>0.0682</v>
       </c>
     </row>
     <row r="11">
@@ -3899,28 +4331,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12540.1</v>
+        <v>4195.4</v>
       </c>
       <c r="E11" t="n">
-        <v>109.219286</v>
+        <v>109.266119</v>
       </c>
       <c r="F11" t="n">
-        <v>23.035553</v>
+        <v>23.010269</v>
       </c>
       <c r="G11" t="n">
-        <v>494.8</v>
+        <v>559</v>
       </c>
       <c r="H11" t="n">
-        <v>13006.6</v>
+        <v>4720.8</v>
       </c>
       <c r="I11" t="n">
-        <v>14435</v>
+        <v>4720.8</v>
       </c>
       <c r="J11" t="n">
-        <v>14705.5</v>
+        <v>5060.9</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5885</v>
+        <v>0.1805</v>
       </c>
     </row>
     <row r="12">
@@ -3936,32 +4368,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>R-P05</t>
+          <t>R-P02</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14337.2</v>
+        <v>4382.4</v>
       </c>
       <c r="E12" t="n">
-        <v>109.262217</v>
+        <v>109.230994</v>
       </c>
       <c r="F12" t="n">
-        <v>23.017493</v>
+        <v>23.010269</v>
       </c>
       <c r="G12" t="n">
-        <v>572.1</v>
+        <v>395.2</v>
       </c>
       <c r="H12" t="n">
-        <v>14837.7</v>
+        <v>4622.3</v>
       </c>
       <c r="I12" t="n">
-        <v>16380.8</v>
+        <v>4622.3</v>
       </c>
       <c r="J12" t="n">
-        <v>16693.4</v>
+        <v>4657.9</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6384</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="13">
@@ -3972,37 +4404,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>R-P06</t>
+          <t>R-P01</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14705.5</v>
+        <v>4657.9</v>
       </c>
       <c r="E13" t="n">
-        <v>109.273925</v>
+        <v>109.203674</v>
       </c>
       <c r="F13" t="n">
         <v>23.039165</v>
       </c>
       <c r="G13" t="n">
-        <v>597.1</v>
+        <v>705.6</v>
       </c>
       <c r="H13" t="n">
-        <v>15354.1</v>
+        <v>5255.1</v>
       </c>
       <c r="I13" t="n">
-        <v>17888.9</v>
+        <v>5255.1</v>
       </c>
       <c r="J13" t="n">
-        <v>18350</v>
+        <v>5673.9</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0357</v>
+        <v>0.2206</v>
       </c>
     </row>
     <row r="14">
@@ -4013,37 +4445,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>R-P01</t>
+          <t>R-P06</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16693.4</v>
+        <v>5060.9</v>
       </c>
       <c r="E14" t="n">
-        <v>109.219286</v>
+        <v>109.207577</v>
       </c>
       <c r="F14" t="n">
-        <v>23.035553</v>
+        <v>23.021105</v>
       </c>
       <c r="G14" t="n">
-        <v>494.8</v>
+        <v>541.6</v>
       </c>
       <c r="H14" t="n">
-        <v>17159.9</v>
+        <v>5511.1</v>
       </c>
       <c r="I14" t="n">
-        <v>18934.8</v>
+        <v>5511.1</v>
       </c>
       <c r="J14" t="n">
-        <v>19205.2</v>
+        <v>5769.9</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6944</v>
+        <v>0.1376</v>
       </c>
     </row>
     <row r="15">
@@ -4054,37 +4486,447 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R-P02</t>
+          <t>R-P05</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18350</v>
+        <v>5673.9</v>
       </c>
       <c r="E15" t="n">
-        <v>109.203674</v>
+        <v>109.219286</v>
       </c>
       <c r="F15" t="n">
         <v>23.017493</v>
       </c>
       <c r="G15" t="n">
-        <v>653.1</v>
+        <v>511.8</v>
       </c>
       <c r="H15" t="n">
-        <v>18838.6</v>
+        <v>6040.1</v>
       </c>
       <c r="I15" t="n">
-        <v>20610.4</v>
+        <v>6040.1</v>
       </c>
       <c r="J15" t="n">
-        <v>20916.1</v>
+        <v>6214.1</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6963</v>
+        <v>0.0848</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RT15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R-P03</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5769.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>109.234897</v>
+      </c>
+      <c r="F16" t="n">
+        <v>23.060836</v>
+      </c>
+      <c r="G16" t="n">
+        <v>552.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6427.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6427.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6896.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.269</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RT16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R-P02</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6214.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>109.234897</v>
+      </c>
+      <c r="F17" t="n">
+        <v>23.060836</v>
+      </c>
+      <c r="G17" t="n">
+        <v>552.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6872</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6872</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7340.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.269</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RT17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R-P04</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6896.1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>109.203674</v>
+      </c>
+      <c r="F18" t="n">
+        <v>23.039165</v>
+      </c>
+      <c r="G18" t="n">
+        <v>705.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7493.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7493.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7912.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2206</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RT18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R-P06</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7340.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>109.219286</v>
+      </c>
+      <c r="F19" t="n">
+        <v>23.035553</v>
+      </c>
+      <c r="G19" t="n">
+        <v>494.8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7806.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7806.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8077.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RT19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R-P01</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7912.1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>109.203674</v>
+      </c>
+      <c r="F20" t="n">
+        <v>23.021105</v>
+      </c>
+      <c r="G20" t="n">
+        <v>614</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8401.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8401.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8705</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1582</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RT20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R-P05</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8077.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>109.203674</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23.039165</v>
+      </c>
+      <c r="G21" t="n">
+        <v>705.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8674.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8674.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9093.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2206</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RT21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R-P03</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>8705</v>
+      </c>
+      <c r="E22" t="n">
+        <v>109.219286</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.006658</v>
+      </c>
+      <c r="G22" t="n">
+        <v>460.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9033.200000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9033.200000000001</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9164.1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0648</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RT22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>R-P02</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>9093.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>109.234897</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.060836</v>
+      </c>
+      <c r="G23" t="n">
+        <v>552.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9751.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>9751.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10219.3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.269</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RT23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>R-P04</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>9164.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>109.2388</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.006658</v>
+      </c>
+      <c r="G24" t="n">
+        <v>440.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9462.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>9462.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9561.700000000001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0473</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RT24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>R-P06</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>9561.700000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>109.219286</v>
+      </c>
+      <c r="F25" t="n">
+        <v>23.017493</v>
+      </c>
+      <c r="G25" t="n">
+        <v>511.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>9928</v>
+      </c>
+      <c r="I25" t="n">
+        <v>9928</v>
+      </c>
+      <c r="J25" t="n">
+        <v>10101.9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0848</v>
       </c>
     </row>
   </sheetData>
@@ -4098,7 +4940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4144,7 +4986,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4156,7 +4998,7 @@
         <v>452.7</v>
       </c>
       <c r="D2" t="n">
-        <v>3051.2</v>
+        <v>1653.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4181,10 +5023,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>525.4</v>
+        <v>500.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3515.3</v>
+        <v>2115.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4209,10 +5051,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3812</v>
+        <v>2369.7</v>
       </c>
       <c r="D4" t="n">
-        <v>5972.6</v>
+        <v>2369.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4237,10 +5079,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4527</v>
+        <v>2764</v>
       </c>
       <c r="D5" t="n">
-        <v>6136.3</v>
+        <v>2764</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4265,10 +5107,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6880.9</v>
+        <v>2873</v>
       </c>
       <c r="D6" t="n">
-        <v>8540.299999999999</v>
+        <v>2873</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4284,7 +5126,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4293,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7109.6</v>
+        <v>3405.5</v>
       </c>
       <c r="D7" t="n">
-        <v>9508.200000000001</v>
+        <v>3405.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4312,7 +5154,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4321,10 +5163,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9257.4</v>
+        <v>3375.1</v>
       </c>
       <c r="D8" t="n">
-        <v>11081.8</v>
+        <v>3375.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4340,7 +5182,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4349,10 +5191,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10469.5</v>
+        <v>4112</v>
       </c>
       <c r="D9" t="n">
-        <v>12071.9</v>
+        <v>4112</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4368,7 +5210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4377,10 +5219,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11631.2</v>
+        <v>4054.4</v>
       </c>
       <c r="D10" t="n">
-        <v>14078.3</v>
+        <v>4054.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4396,7 +5238,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4405,10 +5247,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13006.6</v>
+        <v>4720.8</v>
       </c>
       <c r="D11" t="n">
-        <v>14435</v>
+        <v>4720.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4433,10 +5275,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14837.7</v>
+        <v>4622.3</v>
       </c>
       <c r="D12" t="n">
-        <v>16380.8</v>
+        <v>4622.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4452,7 +5294,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4461,10 +5303,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15354.1</v>
+        <v>5255.1</v>
       </c>
       <c r="D13" t="n">
-        <v>17888.9</v>
+        <v>5255.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4489,10 +5331,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17159.9</v>
+        <v>5511.1</v>
       </c>
       <c r="D14" t="n">
-        <v>18934.8</v>
+        <v>5511.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4508,7 +5350,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4517,10 +5359,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18838.6</v>
+        <v>6040.1</v>
       </c>
       <c r="D15" t="n">
-        <v>20610.4</v>
+        <v>6040.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4530,6 +5372,286 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>RT14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T018</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6427.9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6427.9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>RT15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T019</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6872</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RT16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T020</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7493.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7493.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RT17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7806.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7806.7</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>RT18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8401.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8401.6</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>RT19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8674.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8674.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>RT20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9033.200000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9033.200000000001</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>RT21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9751.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9751.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>RT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T027</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9462.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9462.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>RT23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T028</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>全程</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9928</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9928</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>RT24</t>
         </is>
       </c>
     </row>
@@ -4632,28 +5754,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -4671,28 +5793,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -4713,22 +5835,22 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -4745,23 +5867,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S001|S002|S004|S005|S008|S009|S010|S012|S013</t>
+          <t>S001|S002|S003|S004|S005|S006|S007|S008|S009|S011|S012|S013|S015</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -4770,7 +5892,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4784,29 +5906,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S003|S006|S007|S011</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -4830,22 +5952,22 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>

--- a/otheragent/results/结果提交文件.xlsx
+++ b/otheragent/results/结果提交文件.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/otheragent/results/结果提交文件.xlsx
+++ b/otheragent/results/结果提交文件.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1156,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1237,14 +1237,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S001→S009→S002</t>
+          <t>S002→S012</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2683.8</v>
+        <v>2563.8</v>
       </c>
       <c r="H2" t="n">
-        <v>5.75837</v>
+        <v>6.39651</v>
       </c>
     </row>
     <row r="3">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2297.1</v>
+        <v>2429.1</v>
       </c>
       <c r="H3" t="n">
-        <v>5.61535</v>
+        <v>5.9659</v>
       </c>
     </row>
     <row r="4">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>A-B01</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1309,14 +1309,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S013→S012</t>
+          <t>S006→S007</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2143.3</v>
+        <v>2054.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.68289</v>
+        <v>2.20346</v>
       </c>
     </row>
     <row r="5">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>B-B01</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1345,14 +1345,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S001→S012</t>
+          <t>S001→S013</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2115.1</v>
+        <v>1778.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.55544</v>
+        <v>1.96602</v>
       </c>
     </row>
     <row r="6">
@@ -1363,17 +1363,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A-B01</t>
+          <t>B-B02</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1381,14 +1381,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1713.5</v>
+        <v>1861.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.89948</v>
+        <v>2.13643</v>
       </c>
     </row>
     <row r="7">
@@ -1417,14 +1417,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1650.4</v>
+        <v>1713.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89044</v>
+        <v>1.89948</v>
       </c>
     </row>
     <row r="8">
@@ -1453,14 +1453,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1606.4</v>
+        <v>1311.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.89322</v>
+        <v>1.31031</v>
       </c>
     </row>
     <row r="9">
@@ -1489,14 +1489,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S013→S012</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1653.5</v>
+        <v>2334.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8668</v>
+        <v>2.98356</v>
       </c>
     </row>
     <row r="10">
@@ -1521,18 +1521,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1606.4</v>
+        <v>1311.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3196.9</v>
+        <v>3490.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.91929</v>
+        <v>3.08691</v>
       </c>
     </row>
     <row r="11">
@@ -1557,18 +1557,18 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1650.4</v>
+        <v>1713.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2958.5</v>
+        <v>3876.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.26313</v>
+        <v>3.19648</v>
       </c>
     </row>
     <row r="12">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1593,18 +1593,18 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2115.1</v>
+        <v>1778.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3976.2</v>
+        <v>3329.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.13643</v>
+        <v>1.82113</v>
       </c>
     </row>
     <row r="13">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2143.3</v>
+        <v>1861.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3348.2</v>
+        <v>3065.9</v>
       </c>
       <c r="H13" t="n">
         <v>1.2923</v>
@@ -1651,32 +1651,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C-B03</t>
+          <t>A-B03</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2297.1</v>
+        <v>2189.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S001→S009</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4397</v>
+        <v>4352.4</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2936</v>
+        <v>3.3049</v>
       </c>
     </row>
     <row r="15">
@@ -1687,32 +1687,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2653.3</v>
+        <v>2429.1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3964.4</v>
+        <v>3853.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.31031</v>
+        <v>2.51962</v>
       </c>
     </row>
     <row r="16">
@@ -1737,18 +1737,18 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2683.8</v>
+        <v>2563.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S011→S015→S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5370.2</v>
+        <v>3856.5</v>
       </c>
       <c r="H16" t="n">
-        <v>4.52496</v>
+        <v>2.01897</v>
       </c>
     </row>
     <row r="17">
@@ -1769,22 +1769,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A-B04</t>
+          <t>A-B02</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2692.8</v>
+        <v>2762.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S005→S008</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5120.4</v>
+        <v>5012.8</v>
       </c>
       <c r="H17" t="n">
-        <v>3.33864</v>
+        <v>2.95919</v>
       </c>
     </row>
     <row r="18">
@@ -1795,32 +1795,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A-B01</t>
+          <t>B-B01</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2958.5</v>
+        <v>3297.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S009→S002</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5209</v>
+        <v>5322.1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9768</v>
+        <v>2.49745</v>
       </c>
     </row>
     <row r="19">
@@ -1831,32 +1831,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A-B02</t>
+          <t>B-B02</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3196.9</v>
+        <v>3453.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S011→S001</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5376</v>
+        <v>5014.3</v>
       </c>
       <c r="H19" t="n">
-        <v>3.08691</v>
+        <v>1.48461</v>
       </c>
     </row>
     <row r="20">
@@ -1867,32 +1867,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3889.1</v>
+        <v>4878.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S011→S015→S003</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5811.1</v>
+        <v>7947.7</v>
       </c>
       <c r="H20" t="n">
-        <v>3.03546</v>
+        <v>6.10217</v>
       </c>
     </row>
     <row r="21">
@@ -1903,32 +1903,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A-B06</t>
+          <t>B-B03</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3964.4</v>
+        <v>5014.3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>6127.2</v>
+        <v>6936.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0712</v>
+        <v>3.03546</v>
       </c>
     </row>
     <row r="22">
@@ -1939,32 +1939,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3976.2</v>
+        <v>5129.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S007→S003→S006</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5730</v>
+        <v>8102</v>
       </c>
       <c r="H22" t="n">
-        <v>2.40615</v>
+        <v>6.11788</v>
       </c>
     </row>
     <row r="23">
@@ -1975,32 +1975,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C-B02</t>
+          <t>B-B04</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4651.3</v>
+        <v>5322.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>S006→S003→S007</t>
+          <t>S001→S005</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7689.8</v>
+        <v>7149.7</v>
       </c>
       <c r="H23" t="n">
-        <v>6.39125</v>
+        <v>2.03505</v>
       </c>
     </row>
     <row r="24">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A-B03</t>
+          <t>B-B02</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5120.4</v>
+        <v>6936.3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>7283.1</v>
+        <v>8433.700000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>3.3049</v>
+        <v>1.99976</v>
       </c>
     </row>
     <row r="25">
@@ -2047,32 +2047,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A-B05</t>
+          <t>B-B01</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5209</v>
+        <v>7149.7</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S005→S008</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>7172.8</v>
+        <v>9303.9</v>
       </c>
       <c r="H25" t="n">
-        <v>2.46994</v>
+        <v>2.60821</v>
       </c>
     </row>
     <row r="26">
@@ -2093,130 +2093,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C-B01</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5370.2</v>
+        <v>7947.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>S005→S004</t>
+          <t>S005→S004→S002</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>7883.4</v>
+        <v>10855.1</v>
       </c>
       <c r="H26" t="n">
-        <v>5.56312</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>5730</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>6876.3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.02534</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>T027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>B-B04</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5811.1</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>7325.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.77089</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>T028</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>U01</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>A-B01</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>6569</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>8819.5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.95919</v>
+        <v>6.35986</v>
       </c>
     </row>
   </sheetData>
@@ -2269,7 +2161,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2278,7 +2170,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1066.5</v>
+        <v>6178.3</v>
       </c>
     </row>
     <row r="3">
@@ -2289,7 +2181,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2298,7 +2190,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6586.3</v>
+        <v>856.3</v>
       </c>
     </row>
     <row r="4">
@@ -2309,7 +2201,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2318,7 +2210,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6586.3</v>
+        <v>4724.3</v>
       </c>
     </row>
     <row r="5">
@@ -2329,7 +2221,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2338,7 +2230,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>826.3</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="6">
@@ -2349,7 +2241,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2358,7 +2250,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3405.7</v>
+        <v>3543.7</v>
       </c>
     </row>
     <row r="7">
@@ -2369,7 +2261,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2378,7 +2270,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2617.6</v>
+        <v>3546.3</v>
       </c>
     </row>
     <row r="8">
@@ -2389,7 +2281,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2398,7 +2290,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2617.6</v>
+        <v>3546.3</v>
       </c>
     </row>
     <row r="9">
@@ -2409,7 +2301,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2418,7 +2310,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2617.6</v>
+        <v>3546.3</v>
       </c>
     </row>
     <row r="10">
@@ -2429,7 +2321,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2438,7 +2330,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1042.5</v>
+        <v>3543.7</v>
       </c>
     </row>
     <row r="11">
@@ -2449,7 +2341,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2458,7 +2350,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3405.7</v>
+        <v>3543.7</v>
       </c>
     </row>
     <row r="12">
@@ -2469,7 +2361,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2478,7 +2370,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3405.7</v>
+        <v>3543.7</v>
       </c>
     </row>
     <row r="13">
@@ -2489,7 +2381,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2498,7 +2390,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3405.7</v>
+        <v>3543.7</v>
       </c>
     </row>
     <row r="14">
@@ -2518,7 +2410,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1042.5</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="15">
@@ -2538,7 +2430,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1042.5</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="16">
@@ -2549,7 +2441,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2558,7 +2450,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1066.5</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="17">
@@ -2569,7 +2461,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,7 +2470,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5135</v>
+        <v>4727.1</v>
       </c>
     </row>
     <row r="18">
@@ -2589,7 +2481,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2598,7 +2490,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5135</v>
+        <v>4727.1</v>
       </c>
     </row>
     <row r="19">
@@ -2609,7 +2501,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2618,7 +2510,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2065</v>
+        <v>10236.4</v>
       </c>
     </row>
     <row r="20">
@@ -2629,7 +2521,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2638,7 +2530,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2065</v>
+        <v>1810.4</v>
       </c>
     </row>
     <row r="21">
@@ -2649,7 +2541,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2658,7 +2550,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2065</v>
+        <v>1810.4</v>
       </c>
     </row>
     <row r="22">
@@ -2669,7 +2561,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2678,7 +2570,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2065</v>
+        <v>1810.4</v>
       </c>
     </row>
     <row r="23">
@@ -2689,7 +2581,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2698,7 +2590,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1678.4</v>
+        <v>1281.6</v>
       </c>
     </row>
     <row r="24">
@@ -2709,7 +2601,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2718,7 +2610,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1678.4</v>
+        <v>1281.6</v>
       </c>
     </row>
     <row r="25">
@@ -2729,7 +2621,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T028</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2738,7 +2630,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7972.2</v>
+        <v>4165.5</v>
       </c>
     </row>
     <row r="26">
@@ -2749,7 +2641,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T028</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2758,7 +2650,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7972.2</v>
+        <v>4165.5</v>
       </c>
     </row>
     <row r="27">
@@ -2769,7 +2661,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2778,7 +2670,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6685.6</v>
+        <v>7164.5</v>
       </c>
     </row>
     <row r="28">
@@ -2789,7 +2681,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2798,7 +2690,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4361.7</v>
+        <v>7164.5</v>
       </c>
     </row>
     <row r="29">
@@ -2809,7 +2701,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2818,7 +2710,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4361.7</v>
+        <v>7164.5</v>
       </c>
     </row>
     <row r="30">
@@ -2829,7 +2721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2838,7 +2730,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6685.6</v>
+        <v>6916.7</v>
       </c>
     </row>
     <row r="31">
@@ -2849,7 +2741,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2858,7 +2750,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6685.6</v>
+        <v>6916.7</v>
       </c>
     </row>
     <row r="32">
@@ -2869,7 +2761,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2878,7 +2770,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6685.6</v>
+        <v>6916.7</v>
       </c>
     </row>
     <row r="33">
@@ -2898,7 +2790,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7165.6</v>
+        <v>9773.1</v>
       </c>
     </row>
     <row r="34">
@@ -2918,7 +2810,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7165.6</v>
+        <v>9773.1</v>
       </c>
     </row>
     <row r="35">
@@ -2929,7 +2821,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2938,7 +2830,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4568.1</v>
+        <v>2682.3</v>
       </c>
     </row>
     <row r="36">
@@ -2949,7 +2841,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2958,7 +2850,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4568.1</v>
+        <v>2682.3</v>
       </c>
     </row>
     <row r="37">
@@ -2969,7 +2861,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2978,7 +2870,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5131.8</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="38">
@@ -2989,7 +2881,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2998,7 +2890,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5131.8</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="39">
@@ -3009,7 +2901,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3018,7 +2910,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3790.9</v>
+        <v>8159.7</v>
       </c>
     </row>
     <row r="40">
@@ -3038,7 +2930,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6604.4</v>
+        <v>9212</v>
       </c>
     </row>
     <row r="41">
@@ -3049,7 +2941,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>T027</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3058,7 +2950,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6851.2</v>
+        <v>6675.1</v>
       </c>
     </row>
     <row r="42">
@@ -3069,7 +2961,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>T027</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3078,7 +2970,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6851.2</v>
+        <v>6675.1</v>
       </c>
     </row>
     <row r="43">
@@ -3098,7 +2990,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6604.4</v>
+        <v>9212</v>
       </c>
     </row>
     <row r="44">
@@ -3118,7 +3010,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6604.4</v>
+        <v>9212</v>
       </c>
     </row>
     <row r="45">
@@ -3129,7 +3021,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3138,7 +3030,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5745.3</v>
+        <v>904.3</v>
       </c>
     </row>
     <row r="46">
@@ -3149,7 +3041,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3158,7 +3050,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5745.3</v>
+        <v>7751.4</v>
       </c>
     </row>
     <row r="47">
@@ -3169,7 +3061,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3178,7 +3070,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3587.6</v>
+        <v>934.3</v>
       </c>
     </row>
     <row r="48">
@@ -3189,7 +3081,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3198,7 +3090,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3587.6</v>
+        <v>934.3</v>
       </c>
     </row>
     <row r="49">
@@ -3218,7 +3110,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3024.5</v>
+        <v>2742.3</v>
       </c>
     </row>
     <row r="50">
@@ -3238,7 +3130,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3024.5</v>
+        <v>2742.3</v>
       </c>
     </row>
     <row r="51">
@@ -3249,7 +3141,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3258,7 +3150,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4818.9</v>
+        <v>6390.8</v>
       </c>
     </row>
     <row r="52">
@@ -3269,7 +3161,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3278,7 +3170,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7138.5</v>
+        <v>6390.8</v>
       </c>
     </row>
     <row r="53">
@@ -3289,7 +3181,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3309,7 +3201,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3329,7 +3221,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3338,7 +3230,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1074.4</v>
+        <v>1475.3</v>
       </c>
     </row>
     <row r="56">
@@ -3349,7 +3241,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3358,7 +3250,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6482</v>
+        <v>3551.2</v>
       </c>
     </row>
     <row r="57">
@@ -3369,7 +3261,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T024</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3378,7 +3270,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5326</v>
+        <v>8637.4</v>
       </c>
     </row>
     <row r="58">
@@ -3389,7 +3281,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3398,7 +3290,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5326</v>
+        <v>3075.1</v>
       </c>
     </row>
     <row r="59">
@@ -3409,7 +3301,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3418,7 +3310,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4319.2</v>
+        <v>3075.1</v>
       </c>
     </row>
     <row r="60">
@@ -3429,7 +3321,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3438,7 +3330,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6482</v>
+        <v>3551.2</v>
       </c>
     </row>
     <row r="61">
@@ -3449,7 +3341,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T023</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3458,7 +3350,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1534.2</v>
+        <v>7966.6</v>
       </c>
     </row>
     <row r="62">
@@ -3469,7 +3361,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3478,7 +3370,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3909.3</v>
+        <v>4327.3</v>
       </c>
     </row>
     <row r="63">
@@ -3489,7 +3381,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T023</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3498,7 +3390,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3909.3</v>
+        <v>7966.6</v>
       </c>
     </row>
     <row r="64">
@@ -3509,7 +3401,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3518,7 +3410,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1102.8</v>
+        <v>2861.5</v>
       </c>
     </row>
     <row r="65">
@@ -3529,7 +3421,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3538,7 +3430,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1102.8</v>
+        <v>2861.5</v>
       </c>
     </row>
     <row r="66">
@@ -3549,7 +3441,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3558,7 +3450,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2649.2</v>
+        <v>2861.5</v>
       </c>
     </row>
     <row r="67">
@@ -3569,7 +3461,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3578,7 +3470,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3715.6</v>
+        <v>5898.1</v>
       </c>
     </row>
     <row r="68">
@@ -3589,7 +3481,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3598,7 +3490,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3715.6</v>
+        <v>4328.3</v>
       </c>
     </row>
     <row r="69">
@@ -3609,7 +3501,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3618,7 +3510,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3715.6</v>
+        <v>4328.3</v>
       </c>
     </row>
     <row r="70">
@@ -3629,7 +3521,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3638,7 +3530,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1491.8</v>
+        <v>1560.2</v>
       </c>
     </row>
     <row r="71">
@@ -3649,7 +3541,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3658,7 +3550,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1491.8</v>
+        <v>1874.9</v>
       </c>
     </row>
     <row r="72">
@@ -3669,7 +3561,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3678,7 +3570,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1463.6</v>
+        <v>1874.9</v>
       </c>
     </row>
     <row r="73">
@@ -3689,7 +3581,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3698,7 +3590,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1080.7</v>
+        <v>1050.7</v>
       </c>
     </row>
     <row r="74">
@@ -3709,7 +3601,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3718,7 +3610,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1080.7</v>
+        <v>1333.6</v>
       </c>
     </row>
     <row r="75">
@@ -3729,7 +3621,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3738,7 +3630,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>999.9</v>
+        <v>1333.6</v>
       </c>
     </row>
     <row r="76">
@@ -3749,7 +3641,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3758,7 +3650,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3353.2</v>
+        <v>1238.1</v>
       </c>
     </row>
     <row r="77">
@@ -3769,7 +3661,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3778,7 +3670,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3353.2</v>
+        <v>1238.1</v>
       </c>
     </row>
     <row r="78">
@@ -3789,7 +3681,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3798,7 +3690,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3353.2</v>
+        <v>1238.1</v>
       </c>
     </row>
     <row r="79">
@@ -3809,7 +3701,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3818,7 +3710,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4368.3</v>
+        <v>6622.7</v>
       </c>
     </row>
     <row r="80">
@@ -3829,7 +3721,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>T024</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3838,7 +3730,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6464.3</v>
+        <v>6622.7</v>
       </c>
     </row>
     <row r="81">
@@ -3849,7 +3741,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T024</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3858,7 +3750,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6464.3</v>
+        <v>6622.7</v>
       </c>
     </row>
   </sheetData>
@@ -3872,7 +3764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3965,25 +3857,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>109.215383</v>
+        <v>109.207577</v>
       </c>
       <c r="F2" t="n">
-        <v>23.028329</v>
+        <v>23.021105</v>
       </c>
       <c r="G2" t="n">
-        <v>562.1</v>
+        <v>541.6</v>
       </c>
       <c r="H2" t="n">
-        <v>452.7</v>
+        <v>450.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1653.5</v>
+        <v>2054.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1917</v>
+        <v>2313.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5044</v>
+        <v>0.6278</v>
       </c>
     </row>
     <row r="3">
@@ -4006,25 +3898,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>109.262217</v>
+        <v>109.215383</v>
       </c>
       <c r="F3" t="n">
-        <v>23.017493</v>
+        <v>23.028329</v>
       </c>
       <c r="G3" t="n">
-        <v>572.1</v>
+        <v>562.1</v>
       </c>
       <c r="H3" t="n">
-        <v>500.5</v>
+        <v>452.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2115.1</v>
+        <v>1713.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2427.7</v>
+        <v>1977</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6602</v>
+        <v>0.5227000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -4035,7 +3927,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4044,28 +3936,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1917</v>
+        <v>1977</v>
       </c>
       <c r="E4" t="n">
-        <v>109.215383</v>
+        <v>109.262217</v>
       </c>
       <c r="F4" t="n">
-        <v>23.028329</v>
+        <v>23.017493</v>
       </c>
       <c r="G4" t="n">
-        <v>562.1</v>
+        <v>572.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2369.7</v>
+        <v>2477.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2369.7</v>
+        <v>2477.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2633.1</v>
+        <v>2790.1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1374</v>
+        <v>0.1669</v>
       </c>
     </row>
     <row r="5">
@@ -4076,7 +3968,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4085,28 +3977,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2427.7</v>
+        <v>2313.2</v>
       </c>
       <c r="E5" t="n">
-        <v>109.242702</v>
+        <v>109.230994</v>
       </c>
       <c r="F5" t="n">
-        <v>23.006658</v>
+        <v>23.010269</v>
       </c>
       <c r="G5" t="n">
-        <v>504.3</v>
+        <v>395.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2764</v>
+        <v>2553.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2764</v>
+        <v>2553.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2905</v>
+        <v>2588.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0682</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="6">
@@ -4126,28 +4018,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2633.1</v>
+        <v>2588.7</v>
       </c>
       <c r="E6" t="n">
-        <v>109.230994</v>
+        <v>109.266119</v>
       </c>
       <c r="F6" t="n">
         <v>23.010269</v>
       </c>
       <c r="G6" t="n">
-        <v>395.2</v>
+        <v>559</v>
       </c>
       <c r="H6" t="n">
-        <v>2873</v>
+        <v>3114.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2873</v>
+        <v>3114.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2908.6</v>
+        <v>3454.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0143</v>
+        <v>0.1805</v>
       </c>
     </row>
     <row r="7">
@@ -4167,28 +4059,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2905</v>
+        <v>2790.1</v>
       </c>
       <c r="E7" t="n">
-        <v>109.262217</v>
+        <v>109.273925</v>
       </c>
       <c r="F7" t="n">
-        <v>23.017493</v>
+        <v>23.031941</v>
       </c>
       <c r="G7" t="n">
-        <v>572.1</v>
+        <v>562.3</v>
       </c>
       <c r="H7" t="n">
-        <v>3405.5</v>
+        <v>3409.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3405.5</v>
+        <v>3409.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3718.1</v>
+        <v>3842.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1669</v>
+        <v>0.2424</v>
       </c>
     </row>
     <row r="8">
@@ -4204,11 +4096,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>R-P01</t>
+          <t>R-P04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2908.6</v>
+        <v>3454.2</v>
       </c>
       <c r="E8" t="n">
         <v>109.219286</v>
@@ -4220,13 +4112,13 @@
         <v>494.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3375.1</v>
+        <v>3920.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3375.1</v>
+        <v>3920.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3645.5</v>
+        <v>4191.1</v>
       </c>
       <c r="K8" t="n">
         <v>0.152</v>
@@ -4240,37 +4132,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>R-P03</t>
+          <t>R-P02</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3645.5</v>
+        <v>3842.4</v>
       </c>
       <c r="E9" t="n">
-        <v>109.219286</v>
+        <v>109.234897</v>
       </c>
       <c r="F9" t="n">
-        <v>23.035553</v>
+        <v>23.060836</v>
       </c>
       <c r="G9" t="n">
-        <v>494.8</v>
+        <v>552.3</v>
       </c>
       <c r="H9" t="n">
-        <v>4112</v>
+        <v>4500.3</v>
       </c>
       <c r="I9" t="n">
-        <v>4112</v>
+        <v>4500.3</v>
       </c>
       <c r="J9" t="n">
-        <v>4382.4</v>
+        <v>4968.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.152</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="10">
@@ -4281,37 +4173,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>R-P05</t>
+          <t>R-P01</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3718.1</v>
+        <v>4191.1</v>
       </c>
       <c r="E10" t="n">
-        <v>109.242702</v>
+        <v>109.203674</v>
       </c>
       <c r="F10" t="n">
-        <v>23.006658</v>
+        <v>23.039165</v>
       </c>
       <c r="G10" t="n">
-        <v>504.3</v>
+        <v>705.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4054.4</v>
+        <v>4788.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4054.4</v>
+        <v>4788.4</v>
       </c>
       <c r="J10" t="n">
-        <v>4195.4</v>
+        <v>5207.1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0682</v>
+        <v>0.2206</v>
       </c>
     </row>
     <row r="11">
@@ -4327,32 +4219,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>R-P04</t>
+          <t>R-P03</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4195.4</v>
+        <v>4968.5</v>
       </c>
       <c r="E11" t="n">
-        <v>109.266119</v>
+        <v>109.242702</v>
       </c>
       <c r="F11" t="n">
-        <v>23.010269</v>
+        <v>23.006658</v>
       </c>
       <c r="G11" t="n">
-        <v>559</v>
+        <v>504.3</v>
       </c>
       <c r="H11" t="n">
-        <v>4720.8</v>
+        <v>5304.8</v>
       </c>
       <c r="I11" t="n">
-        <v>4720.8</v>
+        <v>5304.8</v>
       </c>
       <c r="J11" t="n">
-        <v>5060.9</v>
+        <v>5445.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1805</v>
+        <v>0.0682</v>
       </c>
     </row>
     <row r="12">
@@ -4368,32 +4260,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>R-P02</t>
+          <t>R-P05</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4382.4</v>
+        <v>5207.1</v>
       </c>
       <c r="E12" t="n">
-        <v>109.230994</v>
+        <v>109.203674</v>
       </c>
       <c r="F12" t="n">
-        <v>23.010269</v>
+        <v>23.039165</v>
       </c>
       <c r="G12" t="n">
-        <v>395.2</v>
+        <v>705.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4622.3</v>
+        <v>5804.4</v>
       </c>
       <c r="I12" t="n">
-        <v>4622.3</v>
+        <v>5804.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4657.9</v>
+        <v>6223.1</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0143</v>
+        <v>0.2206</v>
       </c>
     </row>
     <row r="13">
@@ -4404,37 +4296,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>R-P01</t>
+          <t>R-P06</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4657.9</v>
+        <v>5445.8</v>
       </c>
       <c r="E13" t="n">
-        <v>109.203674</v>
+        <v>109.219286</v>
       </c>
       <c r="F13" t="n">
-        <v>23.039165</v>
+        <v>23.017493</v>
       </c>
       <c r="G13" t="n">
-        <v>705.6</v>
+        <v>511.8</v>
       </c>
       <c r="H13" t="n">
-        <v>5255.1</v>
+        <v>5812.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5255.1</v>
+        <v>5812.1</v>
       </c>
       <c r="J13" t="n">
-        <v>5673.9</v>
+        <v>5986</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2206</v>
+        <v>0.0848</v>
       </c>
     </row>
     <row r="14">
@@ -4450,32 +4342,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>R-P06</t>
+          <t>R-P04</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5060.9</v>
+        <v>5986</v>
       </c>
       <c r="E14" t="n">
-        <v>109.207577</v>
+        <v>109.219286</v>
       </c>
       <c r="F14" t="n">
-        <v>23.021105</v>
+        <v>23.035553</v>
       </c>
       <c r="G14" t="n">
-        <v>541.6</v>
+        <v>494.8</v>
       </c>
       <c r="H14" t="n">
-        <v>5511.1</v>
+        <v>6452.5</v>
       </c>
       <c r="I14" t="n">
-        <v>5511.1</v>
+        <v>6452.5</v>
       </c>
       <c r="J14" t="n">
-        <v>5769.9</v>
+        <v>6723</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1376</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="15">
@@ -4491,32 +4383,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R-P05</t>
+          <t>R-P02</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5673.9</v>
+        <v>6223.1</v>
       </c>
       <c r="E15" t="n">
-        <v>109.219286</v>
+        <v>109.234897</v>
       </c>
       <c r="F15" t="n">
-        <v>23.017493</v>
+        <v>23.060836</v>
       </c>
       <c r="G15" t="n">
-        <v>511.8</v>
+        <v>552.3</v>
       </c>
       <c r="H15" t="n">
-        <v>6040.1</v>
+        <v>6881.1</v>
       </c>
       <c r="I15" t="n">
-        <v>6040.1</v>
+        <v>6936.3</v>
       </c>
       <c r="J15" t="n">
-        <v>6214.1</v>
+        <v>7404.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0848</v>
+        <v>0.2859</v>
       </c>
     </row>
     <row r="16">
@@ -4536,28 +4428,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5769.9</v>
+        <v>6723</v>
       </c>
       <c r="E16" t="n">
-        <v>109.234897</v>
+        <v>109.195869</v>
       </c>
       <c r="F16" t="n">
-        <v>23.060836</v>
+        <v>23.021105</v>
       </c>
       <c r="G16" t="n">
-        <v>552.3</v>
+        <v>739.9</v>
       </c>
       <c r="H16" t="n">
-        <v>6427.9</v>
+        <v>7297.2</v>
       </c>
       <c r="I16" t="n">
-        <v>6427.9</v>
+        <v>7947.7</v>
       </c>
       <c r="J16" t="n">
-        <v>6896.1</v>
+        <v>8347.799999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.269</v>
+        <v>0.401</v>
       </c>
     </row>
     <row r="17">
@@ -4573,32 +4465,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>R-P02</t>
+          <t>R-P01</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6214.1</v>
+        <v>7404.5</v>
       </c>
       <c r="E17" t="n">
-        <v>109.234897</v>
+        <v>109.203674</v>
       </c>
       <c r="F17" t="n">
-        <v>23.060836</v>
+        <v>23.021105</v>
       </c>
       <c r="G17" t="n">
-        <v>552.3</v>
+        <v>614</v>
       </c>
       <c r="H17" t="n">
-        <v>6872</v>
+        <v>7894</v>
       </c>
       <c r="I17" t="n">
-        <v>6872</v>
+        <v>8102</v>
       </c>
       <c r="J17" t="n">
-        <v>7340.2</v>
+        <v>8405.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.269</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="18">
@@ -4614,32 +4506,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>R-P04</t>
+          <t>R-P06</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6896.1</v>
+        <v>8347.799999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>109.203674</v>
+        <v>109.2388</v>
       </c>
       <c r="F18" t="n">
-        <v>23.039165</v>
+        <v>23.006658</v>
       </c>
       <c r="G18" t="n">
-        <v>705.6</v>
+        <v>440.6</v>
       </c>
       <c r="H18" t="n">
-        <v>7493.3</v>
+        <v>8646.200000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>7493.3</v>
+        <v>8646.200000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>7912.1</v>
+        <v>8745.4</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2206</v>
+        <v>0.0473</v>
       </c>
     </row>
     <row r="19">
@@ -4655,32 +4547,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R-P06</t>
+          <t>R-P05</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7340.2</v>
+        <v>8405.5</v>
       </c>
       <c r="E19" t="n">
-        <v>109.219286</v>
+        <v>109.230994</v>
       </c>
       <c r="F19" t="n">
-        <v>23.035553</v>
+        <v>23.010269</v>
       </c>
       <c r="G19" t="n">
-        <v>494.8</v>
+        <v>395.2</v>
       </c>
       <c r="H19" t="n">
-        <v>7806.7</v>
+        <v>8645.4</v>
       </c>
       <c r="I19" t="n">
-        <v>7806.7</v>
+        <v>8645.4</v>
       </c>
       <c r="J19" t="n">
-        <v>8077.1</v>
+        <v>8680.9</v>
       </c>
       <c r="K19" t="n">
-        <v>0.152</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="20">
@@ -4691,37 +4583,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>R-P01</t>
+          <t>R-P04</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7912.1</v>
+        <v>8680.9</v>
       </c>
       <c r="E20" t="n">
         <v>109.203674</v>
       </c>
       <c r="F20" t="n">
-        <v>23.021105</v>
+        <v>23.039165</v>
       </c>
       <c r="G20" t="n">
-        <v>614</v>
+        <v>705.6</v>
       </c>
       <c r="H20" t="n">
-        <v>8401.6</v>
+        <v>9278.1</v>
       </c>
       <c r="I20" t="n">
-        <v>8401.6</v>
+        <v>9303.9</v>
       </c>
       <c r="J20" t="n">
-        <v>8705</v>
+        <v>9722.6</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1582</v>
+        <v>0.2285</v>
       </c>
     </row>
     <row r="21">
@@ -4732,201 +4624,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>R-P05</t>
+          <t>R-P02</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8077.1</v>
+        <v>8745.4</v>
       </c>
       <c r="E21" t="n">
-        <v>109.203674</v>
+        <v>109.234897</v>
       </c>
       <c r="F21" t="n">
-        <v>23.039165</v>
+        <v>23.060836</v>
       </c>
       <c r="G21" t="n">
-        <v>705.6</v>
+        <v>552.3</v>
       </c>
       <c r="H21" t="n">
-        <v>8674.4</v>
+        <v>9403.4</v>
       </c>
       <c r="I21" t="n">
-        <v>8674.4</v>
+        <v>10855.1</v>
       </c>
       <c r="J21" t="n">
-        <v>9093.1</v>
+        <v>11323.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2206</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RT21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>R-P03</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8705</v>
-      </c>
-      <c r="E22" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F22" t="n">
-        <v>23.006658</v>
-      </c>
-      <c r="G22" t="n">
-        <v>460.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>9033.200000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>9033.200000000001</v>
-      </c>
-      <c r="J22" t="n">
-        <v>9164.1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0648</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>RT22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>R-P02</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>9093.1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>109.234897</v>
-      </c>
-      <c r="F23" t="n">
-        <v>23.060836</v>
-      </c>
-      <c r="G23" t="n">
-        <v>552.3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>9751.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>9751.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>10219.3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.269</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>RT23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>R-P04</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>9164.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>109.2388</v>
-      </c>
-      <c r="F24" t="n">
-        <v>23.006658</v>
-      </c>
-      <c r="G24" t="n">
-        <v>440.6</v>
-      </c>
-      <c r="H24" t="n">
-        <v>9462.5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>9462.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>9561.700000000001</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.0473</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RT24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>R-P06</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>9561.700000000001</v>
-      </c>
-      <c r="E25" t="n">
-        <v>109.219286</v>
-      </c>
-      <c r="F25" t="n">
-        <v>23.017493</v>
-      </c>
-      <c r="G25" t="n">
-        <v>511.8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>9928</v>
-      </c>
-      <c r="I25" t="n">
-        <v>9928</v>
-      </c>
-      <c r="J25" t="n">
-        <v>10101.9</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.0848</v>
+        <v>0.7126</v>
       </c>
     </row>
   </sheetData>
@@ -4940,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4986,7 +4714,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4995,10 +4723,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>452.7</v>
+        <v>450.2</v>
       </c>
       <c r="D2" t="n">
-        <v>1653.5</v>
+        <v>2054.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -5014,7 +4742,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5023,10 +4751,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>500.5</v>
+        <v>452.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2115.1</v>
+        <v>1713.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -5042,7 +4770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5051,10 +4779,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2369.7</v>
+        <v>2477.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2369.7</v>
+        <v>2477.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -5070,7 +4798,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5079,10 +4807,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2764</v>
+        <v>2553.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2764</v>
+        <v>2553.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -5098,7 +4826,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5107,10 +4835,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2873</v>
+        <v>3114.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2873</v>
+        <v>3114.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -5126,7 +4854,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5135,10 +4863,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3405.5</v>
+        <v>3409.8</v>
       </c>
       <c r="D7" t="n">
-        <v>3405.5</v>
+        <v>3409.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5163,10 +4891,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3375.1</v>
+        <v>3920.7</v>
       </c>
       <c r="D8" t="n">
-        <v>3375.1</v>
+        <v>3920.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5182,7 +4910,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5191,10 +4919,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4112</v>
+        <v>4500.3</v>
       </c>
       <c r="D9" t="n">
-        <v>4112</v>
+        <v>4500.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5210,7 +4938,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5219,10 +4947,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4054.4</v>
+        <v>4788.4</v>
       </c>
       <c r="D10" t="n">
-        <v>4054.4</v>
+        <v>4788.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5247,10 +4975,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4720.8</v>
+        <v>5304.8</v>
       </c>
       <c r="D11" t="n">
-        <v>4720.8</v>
+        <v>5304.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -5275,10 +5003,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4622.3</v>
+        <v>5804.4</v>
       </c>
       <c r="D12" t="n">
-        <v>4622.3</v>
+        <v>5804.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -5303,10 +5031,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5255.1</v>
+        <v>5812.1</v>
       </c>
       <c r="D13" t="n">
-        <v>5255.1</v>
+        <v>5812.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -5322,7 +5050,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5331,10 +5059,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5511.1</v>
+        <v>6452.5</v>
       </c>
       <c r="D14" t="n">
-        <v>5511.1</v>
+        <v>6452.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -5350,7 +5078,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5359,10 +5087,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6040.1</v>
+        <v>6881.1</v>
       </c>
       <c r="D15" t="n">
-        <v>6040.1</v>
+        <v>6936.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -5378,7 +5106,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5387,10 +5115,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6427.9</v>
+        <v>7297.2</v>
       </c>
       <c r="D16" t="n">
-        <v>6427.9</v>
+        <v>7947.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -5406,7 +5134,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5415,10 +5143,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6872</v>
+        <v>7894</v>
       </c>
       <c r="D17" t="n">
-        <v>6872</v>
+        <v>8102</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -5434,7 +5162,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5443,10 +5171,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7493.3</v>
+        <v>8646.200000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>7493.3</v>
+        <v>8646.200000000001</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -5462,7 +5190,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5471,10 +5199,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7806.7</v>
+        <v>8645.4</v>
       </c>
       <c r="D19" t="n">
-        <v>7806.7</v>
+        <v>8645.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -5490,7 +5218,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5499,10 +5227,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8401.6</v>
+        <v>9278.1</v>
       </c>
       <c r="D20" t="n">
-        <v>8401.6</v>
+        <v>9303.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -5518,7 +5246,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5527,10 +5255,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8674.4</v>
+        <v>9403.4</v>
       </c>
       <c r="D21" t="n">
-        <v>8674.4</v>
+        <v>10855.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -5540,118 +5268,6 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>RT20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>9033.200000000001</v>
-      </c>
-      <c r="D22" t="n">
-        <v>9033.200000000001</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>RT21</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>9751.1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>9751.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>RT22</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>T027</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>9462.5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9462.5</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>RT23</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>T028</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>全程</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>9928</v>
-      </c>
-      <c r="D25" t="n">
-        <v>9928</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>RT24</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5385,7 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -5808,7 +5424,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -5880,19 +5496,19 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -5910,19 +5526,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
